--- a/output/version3/test/25-15/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1125</v>
+        <v>1089</v>
       </c>
       <c r="C2" t="n">
-        <v>1109</v>
+        <v>1192</v>
       </c>
       <c r="D2" t="n">
-        <v>983</v>
+        <v>1104</v>
       </c>
       <c r="E2" t="n">
-        <v>1071</v>
+        <v>1061</v>
       </c>
       <c r="F2" t="n">
-        <v>1071</v>
+        <v>1123</v>
       </c>
       <c r="G2" t="n">
-        <v>969</v>
+        <v>1063</v>
       </c>
       <c r="H2" t="n">
-        <v>1020</v>
+        <v>1155</v>
       </c>
       <c r="I2" t="n">
-        <v>971</v>
+        <v>1184</v>
       </c>
       <c r="J2" t="n">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="K2" t="n">
-        <v>1022</v>
+        <v>1112</v>
       </c>
       <c r="L2" t="n">
-        <v>1047.1</v>
+        <v>1121.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1059</v>
+        <v>1037</v>
       </c>
       <c r="C3" t="n">
-        <v>983</v>
+        <v>1025</v>
       </c>
       <c r="D3" t="n">
-        <v>1078</v>
+        <v>1011</v>
       </c>
       <c r="E3" t="n">
-        <v>1057</v>
+        <v>993</v>
       </c>
       <c r="F3" t="n">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="G3" t="n">
-        <v>951</v>
+        <v>1051</v>
       </c>
       <c r="H3" t="n">
-        <v>1059</v>
+        <v>1137</v>
       </c>
       <c r="I3" t="n">
-        <v>1041</v>
+        <v>1250</v>
       </c>
       <c r="J3" t="n">
-        <v>934</v>
+        <v>1261</v>
       </c>
       <c r="K3" t="n">
-        <v>1019</v>
+        <v>977</v>
       </c>
       <c r="L3" t="n">
-        <v>1036.4</v>
+        <v>1091.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>913</v>
+        <v>1048</v>
       </c>
       <c r="C4" t="n">
-        <v>1065</v>
+        <v>1023</v>
       </c>
       <c r="D4" t="n">
-        <v>1059</v>
+        <v>1130</v>
       </c>
       <c r="E4" t="n">
-        <v>895</v>
+        <v>1038</v>
       </c>
       <c r="F4" t="n">
-        <v>1072</v>
+        <v>889</v>
       </c>
       <c r="G4" t="n">
-        <v>1027</v>
+        <v>950</v>
       </c>
       <c r="H4" t="n">
-        <v>1065</v>
+        <v>1041</v>
       </c>
       <c r="I4" t="n">
-        <v>1108</v>
+        <v>993</v>
       </c>
       <c r="J4" t="n">
-        <v>956</v>
+        <v>975</v>
       </c>
       <c r="K4" t="n">
-        <v>1074</v>
+        <v>1016</v>
       </c>
       <c r="L4" t="n">
-        <v>1023.4</v>
+        <v>1010.3</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>951</v>
+        <v>881</v>
       </c>
       <c r="C5" t="n">
-        <v>914</v>
+        <v>945</v>
       </c>
       <c r="D5" t="n">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E5" t="n">
-        <v>1002</v>
+        <v>810</v>
       </c>
       <c r="F5" t="n">
-        <v>827</v>
+        <v>993</v>
       </c>
       <c r="G5" t="n">
-        <v>967</v>
+        <v>1059</v>
       </c>
       <c r="H5" t="n">
-        <v>960</v>
+        <v>925</v>
       </c>
       <c r="I5" t="n">
-        <v>930</v>
+        <v>857</v>
       </c>
       <c r="J5" t="n">
-        <v>1114</v>
+        <v>1053</v>
       </c>
       <c r="K5" t="n">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="L5" t="n">
-        <v>962.7</v>
+        <v>949.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1056</v>
       </c>
       <c r="C6" t="n">
-        <v>1103</v>
+        <v>1073</v>
       </c>
       <c r="D6" t="n">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="E6" t="n">
-        <v>1052</v>
+        <v>990</v>
       </c>
       <c r="F6" t="n">
-        <v>1028</v>
+        <v>1112</v>
       </c>
       <c r="G6" t="n">
-        <v>1001</v>
+        <v>1106</v>
       </c>
       <c r="H6" t="n">
-        <v>1046</v>
+        <v>1019</v>
       </c>
       <c r="I6" t="n">
-        <v>1126</v>
+        <v>1089</v>
       </c>
       <c r="J6" t="n">
-        <v>1024</v>
+        <v>970</v>
       </c>
       <c r="K6" t="n">
-        <v>1154</v>
+        <v>1163</v>
       </c>
       <c r="L6" t="n">
-        <v>1073.4</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>982</v>
+        <v>945</v>
       </c>
       <c r="C7" t="n">
-        <v>1032</v>
+        <v>897</v>
       </c>
       <c r="D7" t="n">
-        <v>948</v>
+        <v>1010</v>
       </c>
       <c r="E7" t="n">
-        <v>918</v>
+        <v>1035</v>
       </c>
       <c r="F7" t="n">
-        <v>961</v>
+        <v>985</v>
       </c>
       <c r="G7" t="n">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="H7" t="n">
-        <v>968</v>
+        <v>919</v>
       </c>
       <c r="I7" t="n">
-        <v>1021</v>
+        <v>1104</v>
       </c>
       <c r="J7" t="n">
-        <v>940</v>
+        <v>977</v>
       </c>
       <c r="K7" t="n">
-        <v>943</v>
+        <v>995</v>
       </c>
       <c r="L7" t="n">
-        <v>979.3</v>
+        <v>997.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1031</v>
+        <v>1112</v>
       </c>
       <c r="C8" t="n">
-        <v>877</v>
+        <v>1030</v>
       </c>
       <c r="D8" t="n">
-        <v>1102</v>
+        <v>986</v>
       </c>
       <c r="E8" t="n">
-        <v>1018</v>
+        <v>1062</v>
       </c>
       <c r="F8" t="n">
-        <v>1004</v>
+        <v>954</v>
       </c>
       <c r="G8" t="n">
-        <v>1005</v>
+        <v>1030</v>
       </c>
       <c r="H8" t="n">
-        <v>1036</v>
+        <v>961</v>
       </c>
       <c r="I8" t="n">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="J8" t="n">
-        <v>934</v>
+        <v>1007</v>
       </c>
       <c r="K8" t="n">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="L8" t="n">
-        <v>993.5</v>
+        <v>1006.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1015</v>
+        <v>990</v>
       </c>
       <c r="C9" t="n">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="D9" t="n">
-        <v>925</v>
+        <v>1035</v>
       </c>
       <c r="E9" t="n">
-        <v>958</v>
+        <v>880</v>
       </c>
       <c r="F9" t="n">
-        <v>1012</v>
+        <v>1049</v>
       </c>
       <c r="G9" t="n">
-        <v>940</v>
+        <v>1013</v>
       </c>
       <c r="H9" t="n">
-        <v>986</v>
+        <v>847</v>
       </c>
       <c r="I9" t="n">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="J9" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="K9" t="n">
-        <v>971</v>
+        <v>896</v>
       </c>
       <c r="L9" t="n">
-        <v>968</v>
+        <v>955.9</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>967</v>
+        <v>997</v>
       </c>
       <c r="C10" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1129</v>
+      </c>
+      <c r="E10" t="n">
+        <v>950</v>
+      </c>
+      <c r="F10" t="n">
+        <v>974</v>
+      </c>
+      <c r="G10" t="n">
         <v>1049</v>
       </c>
-      <c r="D10" t="n">
-        <v>1007</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1018</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1186</v>
-      </c>
-      <c r="G10" t="n">
-        <v>949</v>
-      </c>
       <c r="H10" t="n">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>1009</v>
       </c>
       <c r="J10" t="n">
-        <v>1150</v>
+        <v>1062</v>
       </c>
       <c r="K10" t="n">
-        <v>1242</v>
+        <v>1011</v>
       </c>
       <c r="L10" t="n">
-        <v>1057.9</v>
+        <v>1035.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1113</v>
+        <v>1226</v>
       </c>
       <c r="C11" t="n">
-        <v>1014</v>
+        <v>996</v>
       </c>
       <c r="D11" t="n">
-        <v>1067</v>
+        <v>1133</v>
       </c>
       <c r="E11" t="n">
-        <v>1012</v>
+        <v>936</v>
       </c>
       <c r="F11" t="n">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="G11" t="n">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="H11" t="n">
-        <v>984</v>
+        <v>1149</v>
       </c>
       <c r="I11" t="n">
-        <v>1031</v>
+        <v>945</v>
       </c>
       <c r="J11" t="n">
-        <v>1106</v>
+        <v>1001</v>
       </c>
       <c r="K11" t="n">
-        <v>956</v>
+        <v>1019</v>
       </c>
       <c r="L11" t="n">
-        <v>1040.4</v>
+        <v>1054.5</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1027</v>
+        <v>1060</v>
       </c>
       <c r="C12" t="n">
-        <v>1012</v>
+        <v>1211</v>
       </c>
       <c r="D12" t="n">
-        <v>1226</v>
+        <v>1036</v>
       </c>
       <c r="E12" t="n">
-        <v>1130</v>
+        <v>1083</v>
       </c>
       <c r="F12" t="n">
-        <v>1086</v>
+        <v>913</v>
       </c>
       <c r="G12" t="n">
-        <v>1130</v>
+        <v>1197</v>
       </c>
       <c r="H12" t="n">
-        <v>1005</v>
+        <v>1066</v>
       </c>
       <c r="I12" t="n">
-        <v>1154</v>
+        <v>936</v>
       </c>
       <c r="J12" t="n">
-        <v>1188</v>
+        <v>1052</v>
       </c>
       <c r="K12" t="n">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="L12" t="n">
-        <v>1093.6</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1171</v>
+        <v>1110</v>
       </c>
       <c r="C13" t="n">
-        <v>1009</v>
+        <v>1156</v>
       </c>
       <c r="D13" t="n">
-        <v>1176</v>
+        <v>1144</v>
       </c>
       <c r="E13" t="n">
-        <v>1099</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="n">
-        <v>1121</v>
+        <v>1079</v>
       </c>
       <c r="G13" t="n">
-        <v>1196</v>
+        <v>1119</v>
       </c>
       <c r="H13" t="n">
-        <v>1142</v>
+        <v>1013</v>
       </c>
       <c r="I13" t="n">
-        <v>1055</v>
+        <v>1112</v>
       </c>
       <c r="J13" t="n">
-        <v>1054</v>
+        <v>1181</v>
       </c>
       <c r="K13" t="n">
-        <v>1104</v>
+        <v>1254</v>
       </c>
       <c r="L13" t="n">
-        <v>1112.7</v>
+        <v>1137.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>927</v>
+        <v>1023</v>
       </c>
       <c r="C14" t="n">
-        <v>1153</v>
+        <v>958</v>
       </c>
       <c r="D14" t="n">
-        <v>1025</v>
+        <v>907</v>
       </c>
       <c r="E14" t="n">
-        <v>927</v>
+        <v>953</v>
       </c>
       <c r="F14" t="n">
-        <v>980</v>
+        <v>1199</v>
       </c>
       <c r="G14" t="n">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="H14" t="n">
-        <v>868</v>
+        <v>1087</v>
       </c>
       <c r="I14" t="n">
-        <v>1111</v>
+        <v>961</v>
       </c>
       <c r="J14" t="n">
-        <v>938</v>
+        <v>908</v>
       </c>
       <c r="K14" t="n">
-        <v>1186</v>
+        <v>1140</v>
       </c>
       <c r="L14" t="n">
-        <v>1006</v>
+        <v>1006.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>923</v>
+        <v>1038</v>
       </c>
       <c r="C15" t="n">
-        <v>1114</v>
+        <v>1089</v>
       </c>
       <c r="D15" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1102</v>
+      </c>
+      <c r="F15" t="n">
+        <v>917</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1199</v>
+      </c>
+      <c r="H15" t="n">
         <v>1051</v>
       </c>
-      <c r="E15" t="n">
-        <v>1122</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1151</v>
-      </c>
-      <c r="G15" t="n">
-        <v>981</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1041</v>
-      </c>
       <c r="I15" t="n">
-        <v>977</v>
+        <v>1035</v>
       </c>
       <c r="J15" t="n">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="K15" t="n">
-        <v>1063</v>
+        <v>994</v>
       </c>
       <c r="L15" t="n">
-        <v>1044.5</v>
+        <v>1050.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1100</v>
+        <v>986</v>
       </c>
       <c r="C16" t="n">
-        <v>1044</v>
+        <v>1258</v>
       </c>
       <c r="D16" t="n">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E16" t="n">
-        <v>1008</v>
+        <v>1091</v>
       </c>
       <c r="F16" t="n">
-        <v>926</v>
+        <v>1050</v>
       </c>
       <c r="G16" t="n">
-        <v>1212</v>
+        <v>978</v>
       </c>
       <c r="H16" t="n">
-        <v>1049</v>
+        <v>1000</v>
       </c>
       <c r="I16" t="n">
-        <v>1044</v>
+        <v>986</v>
       </c>
       <c r="J16" t="n">
-        <v>1142</v>
+        <v>1035</v>
       </c>
       <c r="K16" t="n">
-        <v>1115</v>
+        <v>969</v>
       </c>
       <c r="L16" t="n">
-        <v>1061.9</v>
+        <v>1033.1</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>998</v>
+        <v>1074</v>
       </c>
       <c r="C17" t="n">
-        <v>1052</v>
+        <v>970</v>
       </c>
       <c r="D17" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1031</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H17" t="n">
+        <v>999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1019</v>
+      </c>
+      <c r="J17" t="n">
         <v>1004</v>
       </c>
-      <c r="E17" t="n">
-        <v>1092</v>
-      </c>
-      <c r="F17" t="n">
-        <v>996</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1039</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1214</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1066</v>
-      </c>
       <c r="K17" t="n">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="L17" t="n">
-        <v>1053.3</v>
+        <v>1041.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1049</v>
+        <v>1225</v>
       </c>
       <c r="C18" t="n">
-        <v>1191</v>
+        <v>1220</v>
       </c>
       <c r="D18" t="n">
-        <v>968</v>
+        <v>1124</v>
       </c>
       <c r="E18" t="n">
-        <v>1186</v>
+        <v>1142</v>
       </c>
       <c r="F18" t="n">
-        <v>1178</v>
+        <v>1077</v>
       </c>
       <c r="G18" t="n">
-        <v>1096</v>
+        <v>994</v>
       </c>
       <c r="H18" t="n">
-        <v>1108</v>
+        <v>921</v>
       </c>
       <c r="I18" t="n">
-        <v>1041</v>
+        <v>1181</v>
       </c>
       <c r="J18" t="n">
-        <v>1128</v>
+        <v>886</v>
       </c>
       <c r="K18" t="n">
-        <v>1126</v>
+        <v>1019</v>
       </c>
       <c r="L18" t="n">
-        <v>1107.1</v>
+        <v>1078.9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1007</v>
+        <v>1144</v>
       </c>
       <c r="C19" t="n">
-        <v>1022</v>
+        <v>1189</v>
       </c>
       <c r="D19" t="n">
-        <v>1080</v>
+        <v>1028</v>
       </c>
       <c r="E19" t="n">
-        <v>1103</v>
+        <v>1124</v>
       </c>
       <c r="F19" t="n">
-        <v>1139</v>
+        <v>1091</v>
       </c>
       <c r="G19" t="n">
-        <v>1103</v>
+        <v>957</v>
       </c>
       <c r="H19" t="n">
-        <v>1002</v>
+        <v>1125</v>
       </c>
       <c r="I19" t="n">
-        <v>1274</v>
+        <v>1144</v>
       </c>
       <c r="J19" t="n">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="K19" t="n">
-        <v>1205</v>
+        <v>970</v>
       </c>
       <c r="L19" t="n">
-        <v>1094.4</v>
+        <v>1077.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1293</v>
+        <v>1060</v>
       </c>
       <c r="C20" t="n">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D20" t="n">
-        <v>1103</v>
+        <v>1139</v>
       </c>
       <c r="E20" t="n">
-        <v>924</v>
+        <v>1013</v>
       </c>
       <c r="F20" t="n">
-        <v>985</v>
+        <v>1395</v>
       </c>
       <c r="G20" t="n">
-        <v>1140</v>
+        <v>1037</v>
       </c>
       <c r="H20" t="n">
-        <v>898</v>
+        <v>1031</v>
       </c>
       <c r="I20" t="n">
-        <v>1088</v>
+        <v>1053</v>
       </c>
       <c r="J20" t="n">
-        <v>1253</v>
+        <v>1052</v>
       </c>
       <c r="K20" t="n">
-        <v>1077</v>
+        <v>1025</v>
       </c>
       <c r="L20" t="n">
-        <v>1073.9</v>
+        <v>1078.7</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1123</v>
+        <v>1083</v>
       </c>
       <c r="C21" t="n">
-        <v>1082</v>
+        <v>1007</v>
       </c>
       <c r="D21" t="n">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="E21" t="n">
-        <v>999</v>
+        <v>1014</v>
       </c>
       <c r="F21" t="n">
-        <v>1233</v>
+        <v>1018</v>
       </c>
       <c r="G21" t="n">
-        <v>1091</v>
+        <v>1129</v>
       </c>
       <c r="H21" t="n">
-        <v>1108</v>
+        <v>1038</v>
       </c>
       <c r="I21" t="n">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="J21" t="n">
-        <v>1133</v>
+        <v>1242</v>
       </c>
       <c r="K21" t="n">
-        <v>1019</v>
+        <v>1113</v>
       </c>
       <c r="L21" t="n">
-        <v>1102.2</v>
+        <v>1089.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1238</v>
+        <v>1146</v>
       </c>
       <c r="C22" t="n">
-        <v>1004</v>
+        <v>1095</v>
       </c>
       <c r="D22" t="n">
-        <v>1091</v>
+        <v>1024</v>
       </c>
       <c r="E22" t="n">
-        <v>1125</v>
+        <v>1230</v>
       </c>
       <c r="F22" t="n">
-        <v>1009</v>
+        <v>1132</v>
       </c>
       <c r="G22" t="n">
-        <v>1137</v>
+        <v>1234</v>
       </c>
       <c r="H22" t="n">
-        <v>1002</v>
+        <v>1075</v>
       </c>
       <c r="I22" t="n">
-        <v>1024</v>
+        <v>1162</v>
       </c>
       <c r="J22" t="n">
-        <v>1238</v>
+        <v>1092</v>
       </c>
       <c r="K22" t="n">
-        <v>1004</v>
+        <v>1232</v>
       </c>
       <c r="L22" t="n">
-        <v>1087.2</v>
+        <v>1142.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1008</v>
+        <v>1023</v>
       </c>
       <c r="C23" t="n">
-        <v>1084</v>
+        <v>1015</v>
       </c>
       <c r="D23" t="n">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="E23" t="n">
-        <v>960</v>
+        <v>1011</v>
       </c>
       <c r="F23" t="n">
-        <v>930</v>
+        <v>1017</v>
       </c>
       <c r="G23" t="n">
-        <v>1015</v>
+        <v>1189</v>
       </c>
       <c r="H23" t="n">
-        <v>1071</v>
+        <v>1044</v>
       </c>
       <c r="I23" t="n">
-        <v>895</v>
+        <v>1020</v>
       </c>
       <c r="J23" t="n">
-        <v>960</v>
+        <v>1113</v>
       </c>
       <c r="K23" t="n">
-        <v>944</v>
+        <v>980</v>
       </c>
       <c r="L23" t="n">
-        <v>984</v>
+        <v>1040.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1082</v>
+        <v>1071</v>
       </c>
       <c r="C24" t="n">
-        <v>1051</v>
+        <v>982</v>
       </c>
       <c r="D24" t="n">
-        <v>1103</v>
+        <v>1043</v>
       </c>
       <c r="E24" t="n">
-        <v>1104</v>
+        <v>1162</v>
       </c>
       <c r="F24" t="n">
-        <v>1111</v>
+        <v>1070</v>
       </c>
       <c r="G24" t="n">
-        <v>984</v>
+        <v>953</v>
       </c>
       <c r="H24" t="n">
-        <v>987</v>
+        <v>1014</v>
       </c>
       <c r="I24" t="n">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="J24" t="n">
-        <v>1001</v>
+        <v>1377</v>
       </c>
       <c r="K24" t="n">
-        <v>1044</v>
+        <v>997</v>
       </c>
       <c r="L24" t="n">
-        <v>1047</v>
+        <v>1066.4</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1098</v>
+        <v>1171</v>
       </c>
       <c r="C25" t="n">
-        <v>1131</v>
+        <v>1113</v>
       </c>
       <c r="D25" t="n">
-        <v>1060</v>
+        <v>1010</v>
       </c>
       <c r="E25" t="n">
-        <v>1153</v>
+        <v>1068</v>
       </c>
       <c r="F25" t="n">
-        <v>1094</v>
+        <v>1081</v>
       </c>
       <c r="G25" t="n">
-        <v>996</v>
+        <v>1073</v>
       </c>
       <c r="H25" t="n">
-        <v>1152</v>
+        <v>1167</v>
       </c>
       <c r="I25" t="n">
-        <v>1259</v>
+        <v>1100</v>
       </c>
       <c r="J25" t="n">
-        <v>1216</v>
+        <v>1317</v>
       </c>
       <c r="K25" t="n">
-        <v>1124</v>
+        <v>1040</v>
       </c>
       <c r="L25" t="n">
-        <v>1128.3</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1186</v>
+        <v>1021</v>
       </c>
       <c r="C26" t="n">
-        <v>985</v>
+        <v>958</v>
       </c>
       <c r="D26" t="n">
+        <v>1091</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F26" t="n">
         <v>995</v>
       </c>
-      <c r="E26" t="n">
-        <v>954</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1037</v>
-      </c>
       <c r="G26" t="n">
-        <v>988</v>
+        <v>974</v>
       </c>
       <c r="H26" t="n">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="I26" t="n">
-        <v>1103</v>
+        <v>979</v>
       </c>
       <c r="J26" t="n">
-        <v>1042</v>
+        <v>916</v>
       </c>
       <c r="K26" t="n">
-        <v>1083</v>
+        <v>949</v>
       </c>
       <c r="L26" t="n">
-        <v>1034.7</v>
+        <v>987.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1051</v>
+        <v>1206</v>
       </c>
       <c r="C27" t="n">
-        <v>1088</v>
+        <v>913</v>
       </c>
       <c r="D27" t="n">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="E27" t="n">
-        <v>1152</v>
+        <v>1294</v>
       </c>
       <c r="F27" t="n">
-        <v>1141</v>
+        <v>1072</v>
       </c>
       <c r="G27" t="n">
-        <v>1375</v>
+        <v>1073</v>
       </c>
       <c r="H27" t="n">
-        <v>1237</v>
+        <v>1065</v>
       </c>
       <c r="I27" t="n">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="J27" t="n">
-        <v>1201</v>
+        <v>1118</v>
       </c>
       <c r="K27" t="n">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="L27" t="n">
-        <v>1154.1</v>
+        <v>1102.2</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C28" t="n">
-        <v>976</v>
+        <v>1198</v>
       </c>
       <c r="D28" t="n">
-        <v>1168</v>
+        <v>962</v>
       </c>
       <c r="E28" t="n">
-        <v>1115</v>
+        <v>1033</v>
       </c>
       <c r="F28" t="n">
-        <v>1080</v>
+        <v>1053</v>
       </c>
       <c r="G28" t="n">
-        <v>1009</v>
+        <v>964</v>
       </c>
       <c r="H28" t="n">
-        <v>977</v>
+        <v>1023</v>
       </c>
       <c r="I28" t="n">
-        <v>970</v>
+        <v>1002</v>
       </c>
       <c r="J28" t="n">
-        <v>907</v>
+        <v>1037</v>
       </c>
       <c r="K28" t="n">
-        <v>1207</v>
+        <v>1064</v>
       </c>
       <c r="L28" t="n">
-        <v>1050.9</v>
+        <v>1042.8</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>995</v>
+        <v>926</v>
       </c>
       <c r="C29" t="n">
-        <v>991</v>
+        <v>967</v>
       </c>
       <c r="D29" t="n">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="E29" t="n">
-        <v>975</v>
+        <v>918</v>
       </c>
       <c r="F29" t="n">
-        <v>968</v>
+        <v>1049</v>
       </c>
       <c r="G29" t="n">
-        <v>1040</v>
+        <v>1080</v>
       </c>
       <c r="H29" t="n">
-        <v>852</v>
+        <v>919</v>
       </c>
       <c r="I29" t="n">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="J29" t="n">
-        <v>883</v>
+        <v>1075</v>
       </c>
       <c r="K29" t="n">
-        <v>1015</v>
+        <v>903</v>
       </c>
       <c r="L29" t="n">
-        <v>975.1</v>
+        <v>986.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>961</v>
+        <v>1010</v>
       </c>
       <c r="C30" t="n">
-        <v>1101</v>
+        <v>1012</v>
       </c>
       <c r="D30" t="n">
-        <v>1088</v>
+        <v>994</v>
       </c>
       <c r="E30" t="n">
-        <v>994</v>
+        <v>924</v>
       </c>
       <c r="F30" t="n">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="G30" t="n">
-        <v>1046</v>
+        <v>1120</v>
       </c>
       <c r="H30" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="I30" t="n">
-        <v>959</v>
+        <v>869</v>
       </c>
       <c r="J30" t="n">
-        <v>906</v>
+        <v>1200</v>
       </c>
       <c r="K30" t="n">
-        <v>909</v>
+        <v>1058</v>
       </c>
       <c r="L30" t="n">
-        <v>1000.2</v>
+        <v>1023.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="C31" t="n">
-        <v>1115</v>
+        <v>1140</v>
       </c>
       <c r="D31" t="n">
-        <v>1007</v>
+        <v>1239</v>
       </c>
       <c r="E31" t="n">
-        <v>1094</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="n">
-        <v>1042</v>
+        <v>1091</v>
       </c>
       <c r="G31" t="n">
-        <v>1088</v>
+        <v>1148</v>
       </c>
       <c r="H31" t="n">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="I31" t="n">
-        <v>1222</v>
+        <v>1033</v>
       </c>
       <c r="J31" t="n">
-        <v>1136</v>
+        <v>885</v>
       </c>
       <c r="K31" t="n">
-        <v>1116</v>
+        <v>1065</v>
       </c>
       <c r="L31" t="n">
-        <v>1107</v>
+        <v>1109.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>866</v>
+        <v>940</v>
       </c>
       <c r="C32" t="n">
-        <v>880</v>
+        <v>1052</v>
       </c>
       <c r="D32" t="n">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E32" t="n">
-        <v>992</v>
+        <v>939</v>
       </c>
       <c r="F32" t="n">
-        <v>1040</v>
+        <v>904</v>
       </c>
       <c r="G32" t="n">
-        <v>1020</v>
+        <v>972</v>
       </c>
       <c r="H32" t="n">
-        <v>867</v>
+        <v>1126</v>
       </c>
       <c r="I32" t="n">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="J32" t="n">
-        <v>1062</v>
+        <v>970</v>
       </c>
       <c r="K32" t="n">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="L32" t="n">
-        <v>970.3</v>
+        <v>986.7</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>971</v>
+        <v>1083</v>
       </c>
       <c r="C33" t="n">
-        <v>1006</v>
+        <v>967</v>
       </c>
       <c r="D33" t="n">
-        <v>896</v>
+        <v>1051</v>
       </c>
       <c r="E33" t="n">
-        <v>1042</v>
+        <v>1018</v>
       </c>
       <c r="F33" t="n">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="G33" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H33" t="n">
-        <v>1076</v>
+        <v>1172</v>
       </c>
       <c r="I33" t="n">
-        <v>1052</v>
+        <v>965</v>
       </c>
       <c r="J33" t="n">
-        <v>1145</v>
+        <v>989</v>
       </c>
       <c r="K33" t="n">
-        <v>1004</v>
+        <v>1135</v>
       </c>
       <c r="L33" t="n">
-        <v>1024.3</v>
+        <v>1045.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1132</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1036</v>
+      </c>
+      <c r="E34" t="n">
+        <v>920</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1095</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1015</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I34" t="n">
         <v>1110</v>
       </c>
-      <c r="C34" t="n">
-        <v>968</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1058</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="J34" t="n">
+        <v>1180</v>
+      </c>
+      <c r="K34" t="n">
         <v>1107</v>
       </c>
-      <c r="F34" t="n">
-        <v>1156</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1010</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1075</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1069</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1184</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1072</v>
-      </c>
       <c r="L34" t="n">
-        <v>1080.9</v>
+        <v>1063.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1075</v>
+        <v>1147</v>
       </c>
       <c r="C35" t="n">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D35" t="n">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E35" t="n">
-        <v>1090</v>
+        <v>1130</v>
       </c>
       <c r="F35" t="n">
-        <v>1056</v>
+        <v>1337</v>
       </c>
       <c r="G35" t="n">
-        <v>995</v>
+        <v>1012</v>
       </c>
       <c r="H35" t="n">
-        <v>1046</v>
+        <v>1107</v>
       </c>
       <c r="I35" t="n">
-        <v>1125</v>
+        <v>1007</v>
       </c>
       <c r="J35" t="n">
-        <v>1098</v>
+        <v>1067</v>
       </c>
       <c r="K35" t="n">
-        <v>1217</v>
+        <v>1059</v>
       </c>
       <c r="L35" t="n">
-        <v>1072</v>
+        <v>1087.8</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1045</v>
+        <v>1157</v>
       </c>
       <c r="C36" t="n">
-        <v>940</v>
+        <v>982</v>
       </c>
       <c r="D36" t="n">
-        <v>1179</v>
+        <v>1009</v>
       </c>
       <c r="E36" t="n">
-        <v>1070</v>
+        <v>937</v>
       </c>
       <c r="F36" t="n">
-        <v>968</v>
+        <v>1214</v>
       </c>
       <c r="G36" t="n">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="H36" t="n">
-        <v>1015</v>
+        <v>1076</v>
       </c>
       <c r="I36" t="n">
+        <v>1008</v>
+      </c>
+      <c r="J36" t="n">
         <v>999</v>
       </c>
-      <c r="J36" t="n">
-        <v>1169</v>
-      </c>
       <c r="K36" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="L36" t="n">
-        <v>1059.4</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1105</v>
+        <v>1143</v>
       </c>
       <c r="C37" t="n">
-        <v>1138</v>
+        <v>1013</v>
       </c>
       <c r="D37" t="n">
-        <v>1071</v>
+        <v>1139</v>
       </c>
       <c r="E37" t="n">
-        <v>1154</v>
+        <v>1038</v>
       </c>
       <c r="F37" t="n">
-        <v>1060</v>
+        <v>1028</v>
       </c>
       <c r="G37" t="n">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="H37" t="n">
-        <v>977</v>
+        <v>1209</v>
       </c>
       <c r="I37" t="n">
-        <v>1120</v>
+        <v>1055</v>
       </c>
       <c r="J37" t="n">
-        <v>1037</v>
+        <v>993</v>
       </c>
       <c r="K37" t="n">
-        <v>1017</v>
+        <v>1095</v>
       </c>
       <c r="L37" t="n">
-        <v>1071.3</v>
+        <v>1075.7</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>887</v>
+        <v>1030</v>
       </c>
       <c r="C38" t="n">
-        <v>1056</v>
+        <v>920</v>
       </c>
       <c r="D38" t="n">
-        <v>1012</v>
+        <v>1069</v>
       </c>
       <c r="E38" t="n">
-        <v>960</v>
+        <v>912</v>
       </c>
       <c r="F38" t="n">
-        <v>963</v>
+        <v>1013</v>
       </c>
       <c r="G38" t="n">
-        <v>967</v>
+        <v>1001</v>
       </c>
       <c r="H38" t="n">
-        <v>1061</v>
+        <v>1216</v>
       </c>
       <c r="I38" t="n">
-        <v>1019</v>
+        <v>992</v>
       </c>
       <c r="J38" t="n">
-        <v>838</v>
+        <v>1076</v>
       </c>
       <c r="K38" t="n">
-        <v>1148</v>
+        <v>1118</v>
       </c>
       <c r="L38" t="n">
-        <v>991.1</v>
+        <v>1034.7</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="C39" t="n">
-        <v>1022</v>
+        <v>1127</v>
       </c>
       <c r="D39" t="n">
-        <v>1127</v>
+        <v>994</v>
       </c>
       <c r="E39" t="n">
-        <v>812</v>
+        <v>927</v>
       </c>
       <c r="F39" t="n">
-        <v>964</v>
+        <v>905</v>
       </c>
       <c r="G39" t="n">
-        <v>974</v>
+        <v>901</v>
       </c>
       <c r="H39" t="n">
-        <v>998</v>
+        <v>1123</v>
       </c>
       <c r="I39" t="n">
-        <v>1139</v>
+        <v>972</v>
       </c>
       <c r="J39" t="n">
-        <v>954</v>
+        <v>1153</v>
       </c>
       <c r="K39" t="n">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="L39" t="n">
-        <v>1013.8</v>
+        <v>1032.7</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C40" t="n">
-        <v>1093</v>
+        <v>1000</v>
       </c>
       <c r="D40" t="n">
-        <v>1041</v>
+        <v>1138</v>
       </c>
       <c r="E40" t="n">
-        <v>959</v>
+        <v>1020</v>
       </c>
       <c r="F40" t="n">
-        <v>944</v>
+        <v>999</v>
       </c>
       <c r="G40" t="n">
-        <v>934</v>
+        <v>1089</v>
       </c>
       <c r="H40" t="n">
-        <v>1087</v>
+        <v>1015</v>
       </c>
       <c r="I40" t="n">
-        <v>997</v>
+        <v>1086</v>
       </c>
       <c r="J40" t="n">
-        <v>920</v>
+        <v>1004</v>
       </c>
       <c r="K40" t="n">
-        <v>1009</v>
+        <v>1039</v>
       </c>
       <c r="L40" t="n">
-        <v>999</v>
+        <v>1039.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>954</v>
+      </c>
+      <c r="C41" t="n">
         <v>1076</v>
       </c>
-      <c r="C41" t="n">
-        <v>1130</v>
-      </c>
       <c r="D41" t="n">
-        <v>995</v>
+        <v>972</v>
       </c>
       <c r="E41" t="n">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="F41" t="n">
-        <v>1184</v>
+        <v>969</v>
       </c>
       <c r="G41" t="n">
-        <v>923</v>
+        <v>988</v>
       </c>
       <c r="H41" t="n">
-        <v>1154</v>
+        <v>1033</v>
       </c>
       <c r="I41" t="n">
-        <v>1043</v>
+        <v>1103</v>
       </c>
       <c r="J41" t="n">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="K41" t="n">
-        <v>862</v>
+        <v>1091</v>
       </c>
       <c r="L41" t="n">
-        <v>1027.5</v>
+        <v>1011.6</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
+        <v>1094</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D42" t="n">
+        <v>920</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1076</v>
+      </c>
+      <c r="F42" t="n">
         <v>1011</v>
       </c>
-      <c r="C42" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1096</v>
-      </c>
-      <c r="E42" t="n">
-        <v>971</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1080</v>
-      </c>
       <c r="G42" t="n">
-        <v>930</v>
+        <v>904</v>
       </c>
       <c r="H42" t="n">
-        <v>1075</v>
+        <v>1044</v>
       </c>
       <c r="I42" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="J42" t="n">
-        <v>934</v>
+        <v>1118</v>
       </c>
       <c r="K42" t="n">
-        <v>1005</v>
+        <v>1034</v>
       </c>
       <c r="L42" t="n">
-        <v>1005</v>
+        <v>1019.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1010</v>
+        <v>1059</v>
       </c>
       <c r="C43" t="n">
-        <v>1002</v>
+        <v>1172</v>
       </c>
       <c r="D43" t="n">
-        <v>1027</v>
+        <v>1064</v>
       </c>
       <c r="E43" t="n">
-        <v>1055</v>
+        <v>1005</v>
       </c>
       <c r="F43" t="n">
-        <v>1108</v>
+        <v>1041</v>
       </c>
       <c r="G43" t="n">
-        <v>1131</v>
+        <v>1006</v>
       </c>
       <c r="H43" t="n">
-        <v>1012</v>
+        <v>988</v>
       </c>
       <c r="I43" t="n">
-        <v>988</v>
+        <v>1062</v>
       </c>
       <c r="J43" t="n">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="K43" t="n">
-        <v>963</v>
+        <v>1036</v>
       </c>
       <c r="L43" t="n">
-        <v>1033.1</v>
+        <v>1049.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1080</v>
+        <v>971</v>
       </c>
       <c r="C44" t="n">
-        <v>1157</v>
+        <v>1324</v>
       </c>
       <c r="D44" t="n">
-        <v>1088</v>
+        <v>992</v>
       </c>
       <c r="E44" t="n">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="F44" t="n">
-        <v>977</v>
+        <v>1016</v>
       </c>
       <c r="G44" t="n">
-        <v>1131</v>
+        <v>1014</v>
       </c>
       <c r="H44" t="n">
-        <v>1100</v>
+        <v>1218</v>
       </c>
       <c r="I44" t="n">
-        <v>1024</v>
+        <v>988</v>
       </c>
       <c r="J44" t="n">
-        <v>1169</v>
+        <v>1047</v>
       </c>
       <c r="K44" t="n">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="L44" t="n">
-        <v>1073.6</v>
+        <v>1057.6</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1100</v>
+        <v>928</v>
       </c>
       <c r="C45" t="n">
-        <v>1093</v>
+        <v>982</v>
       </c>
       <c r="D45" t="n">
-        <v>1043</v>
+        <v>1008</v>
       </c>
       <c r="E45" t="n">
-        <v>1057</v>
+        <v>1175</v>
       </c>
       <c r="F45" t="n">
-        <v>1060</v>
+        <v>929</v>
       </c>
       <c r="G45" t="n">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="H45" t="n">
-        <v>911</v>
+        <v>1039</v>
       </c>
       <c r="I45" t="n">
-        <v>1091</v>
+        <v>1050</v>
       </c>
       <c r="J45" t="n">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="K45" t="n">
-        <v>1129</v>
+        <v>1065</v>
       </c>
       <c r="L45" t="n">
-        <v>1050.3</v>
+        <v>1019.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1082</v>
+        <v>1188</v>
       </c>
       <c r="C46" t="n">
-        <v>996</v>
+        <v>1159</v>
       </c>
       <c r="D46" t="n">
-        <v>1192</v>
+        <v>1172</v>
       </c>
       <c r="E46" t="n">
-        <v>1076</v>
+        <v>1116</v>
       </c>
       <c r="F46" t="n">
-        <v>953</v>
+        <v>1055</v>
       </c>
       <c r="G46" t="n">
-        <v>1140</v>
+        <v>1121</v>
       </c>
       <c r="H46" t="n">
-        <v>1142</v>
+        <v>1053</v>
       </c>
       <c r="I46" t="n">
-        <v>1108</v>
+        <v>1050</v>
       </c>
       <c r="J46" t="n">
-        <v>1041</v>
+        <v>1214</v>
       </c>
       <c r="K46" t="n">
-        <v>1084</v>
+        <v>1061</v>
       </c>
       <c r="L46" t="n">
-        <v>1081.4</v>
+        <v>1118.9</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1141</v>
+        <v>923</v>
       </c>
       <c r="C47" t="n">
-        <v>1150</v>
+        <v>964</v>
       </c>
       <c r="D47" t="n">
-        <v>1057</v>
+        <v>1104</v>
       </c>
       <c r="E47" t="n">
-        <v>1048</v>
+        <v>1102</v>
       </c>
       <c r="F47" t="n">
-        <v>1199</v>
+        <v>1006</v>
       </c>
       <c r="G47" t="n">
-        <v>1004</v>
+        <v>973</v>
       </c>
       <c r="H47" t="n">
-        <v>1177</v>
+        <v>1011</v>
       </c>
       <c r="I47" t="n">
-        <v>1329</v>
+        <v>936</v>
       </c>
       <c r="J47" t="n">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="K47" t="n">
-        <v>1042</v>
+        <v>1225</v>
       </c>
       <c r="L47" t="n">
-        <v>1121.7</v>
+        <v>1030.5</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="C48" t="n">
-        <v>1228</v>
+        <v>1123</v>
       </c>
       <c r="D48" t="n">
-        <v>1055</v>
+        <v>1029</v>
       </c>
       <c r="E48" t="n">
-        <v>973</v>
+        <v>1067</v>
       </c>
       <c r="F48" t="n">
-        <v>982</v>
+        <v>1166</v>
       </c>
       <c r="G48" t="n">
-        <v>1103</v>
+        <v>1188</v>
       </c>
       <c r="H48" t="n">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="I48" t="n">
-        <v>1118</v>
+        <v>1068</v>
       </c>
       <c r="J48" t="n">
-        <v>1104</v>
+        <v>1085</v>
       </c>
       <c r="K48" t="n">
-        <v>990</v>
+        <v>1138</v>
       </c>
       <c r="L48" t="n">
-        <v>1078.7</v>
+        <v>1110.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>949</v>
+        <v>1042</v>
       </c>
       <c r="C49" t="n">
-        <v>967</v>
+        <v>1099</v>
       </c>
       <c r="D49" t="n">
-        <v>1009</v>
+        <v>1049</v>
       </c>
       <c r="E49" t="n">
-        <v>1022</v>
+        <v>959</v>
       </c>
       <c r="F49" t="n">
-        <v>942</v>
+        <v>994</v>
       </c>
       <c r="G49" t="n">
-        <v>1003</v>
+        <v>1143</v>
       </c>
       <c r="H49" t="n">
-        <v>1088</v>
+        <v>1024</v>
       </c>
       <c r="I49" t="n">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="J49" t="n">
-        <v>1072</v>
+        <v>1183</v>
       </c>
       <c r="K49" t="n">
-        <v>958</v>
+        <v>1190</v>
       </c>
       <c r="L49" t="n">
-        <v>1001.4</v>
+        <v>1067.8</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1126</v>
+        <v>930</v>
       </c>
       <c r="C50" t="n">
-        <v>939</v>
+        <v>1099</v>
       </c>
       <c r="D50" t="n">
-        <v>1035</v>
+        <v>1022</v>
       </c>
       <c r="E50" t="n">
-        <v>976</v>
+        <v>1019</v>
       </c>
       <c r="F50" t="n">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="G50" t="n">
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="H50" t="n">
-        <v>1014</v>
+        <v>1070</v>
       </c>
       <c r="I50" t="n">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="J50" t="n">
-        <v>926</v>
+        <v>1042</v>
       </c>
       <c r="K50" t="n">
-        <v>1023</v>
+        <v>1109</v>
       </c>
       <c r="L50" t="n">
-        <v>987.7</v>
+        <v>1019.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>942</v>
+        <v>1008</v>
       </c>
       <c r="C51" t="n">
-        <v>1079</v>
+        <v>933</v>
       </c>
       <c r="D51" t="n">
-        <v>955</v>
+        <v>985</v>
       </c>
       <c r="E51" t="n">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="F51" t="n">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G51" t="n">
-        <v>934</v>
+        <v>977</v>
       </c>
       <c r="H51" t="n">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="I51" t="n">
-        <v>1083</v>
+        <v>1072</v>
       </c>
       <c r="J51" t="n">
-        <v>973</v>
+        <v>1114</v>
       </c>
       <c r="K51" t="n">
-        <v>923</v>
+        <v>997</v>
       </c>
       <c r="L51" t="n">
-        <v>993.9</v>
+        <v>1016.8</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1050.06</v>
+        <v>1056.44</v>
       </c>
       <c r="C52" t="n">
-        <v>1042.98</v>
+        <v>1057.4</v>
       </c>
       <c r="D52" t="n">
-        <v>1050.8</v>
+        <v>1048.3</v>
       </c>
       <c r="E52" t="n">
-        <v>1030.54</v>
+        <v>1037</v>
       </c>
       <c r="F52" t="n">
-        <v>1048.6</v>
+        <v>1051.32</v>
       </c>
       <c r="G52" t="n">
-        <v>1034.4</v>
+        <v>1045.14</v>
       </c>
       <c r="H52" t="n">
-        <v>1039.4</v>
+        <v>1051.64</v>
       </c>
       <c r="I52" t="n">
-        <v>1050.5</v>
+        <v>1027.88</v>
       </c>
       <c r="J52" t="n">
-        <v>1047.84</v>
+        <v>1066.2</v>
       </c>
       <c r="K52" t="n">
-        <v>1052.2</v>
+        <v>1058.08</v>
       </c>
       <c r="L52" t="n">
-        <v>1044.732</v>
+        <v>1049.94</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12.92693829536438</v>
+        <v>13.00984144210815</v>
       </c>
       <c r="C2" t="n">
-        <v>12.02873229980469</v>
+        <v>13.13798403739929</v>
       </c>
       <c r="D2" t="n">
-        <v>11.70108580589294</v>
+        <v>13.4497594833374</v>
       </c>
       <c r="E2" t="n">
-        <v>11.62575912475586</v>
+        <v>12.07322525978088</v>
       </c>
       <c r="F2" t="n">
-        <v>11.53453755378723</v>
+        <v>12.37699151039124</v>
       </c>
       <c r="G2" t="n">
-        <v>12.10105299949646</v>
+        <v>12.53358793258667</v>
       </c>
       <c r="H2" t="n">
-        <v>11.35698580741882</v>
+        <v>12.79343175888062</v>
       </c>
       <c r="I2" t="n">
-        <v>13.30601668357849</v>
+        <v>14.34701085090637</v>
       </c>
       <c r="J2" t="n">
-        <v>15.22553133964539</v>
+        <v>13.4866201877594</v>
       </c>
       <c r="K2" t="n">
-        <v>15.70143938064575</v>
+        <v>13.29917144775391</v>
       </c>
       <c r="L2" t="n">
-        <v>12.750807929039</v>
+        <v>13.05076239109039</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>18.45307779312134</v>
+        <v>11.51015830039978</v>
       </c>
       <c r="C3" t="n">
-        <v>11.46930909156799</v>
+        <v>11.46131110191345</v>
       </c>
       <c r="D3" t="n">
-        <v>11.60196614265442</v>
+        <v>12.78661036491394</v>
       </c>
       <c r="E3" t="n">
-        <v>13.97761106491089</v>
+        <v>12.15649366378784</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6323983669281</v>
+        <v>14.40229868888855</v>
       </c>
       <c r="G3" t="n">
-        <v>10.57997465133667</v>
+        <v>11.29163122177124</v>
       </c>
       <c r="H3" t="n">
-        <v>11.45270013809204</v>
+        <v>12.79024577140808</v>
       </c>
       <c r="I3" t="n">
-        <v>10.82289457321167</v>
+        <v>14.82441473007202</v>
       </c>
       <c r="J3" t="n">
-        <v>10.21644067764282</v>
+        <v>15.62691235542297</v>
       </c>
       <c r="K3" t="n">
-        <v>11.3449912071228</v>
+        <v>11.99143719673157</v>
       </c>
       <c r="L3" t="n">
-        <v>12.05513637065888</v>
+        <v>12.88415133953094</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>11.82029271125793</v>
+        <v>13.60930943489075</v>
       </c>
       <c r="C4" t="n">
-        <v>12.70544791221619</v>
+        <v>13.15095496177673</v>
       </c>
       <c r="D4" t="n">
-        <v>13.07799386978149</v>
+        <v>12.90366578102112</v>
       </c>
       <c r="E4" t="n">
-        <v>11.81229281425476</v>
+        <v>13.91500306129456</v>
       </c>
       <c r="F4" t="n">
-        <v>13.07391262054443</v>
+        <v>12.21888399124146</v>
       </c>
       <c r="G4" t="n">
-        <v>14.69206571578979</v>
+        <v>13.5195643901825</v>
       </c>
       <c r="H4" t="n">
-        <v>11.51518774032593</v>
+        <v>12.43878984451294</v>
       </c>
       <c r="I4" t="n">
-        <v>14.48915815353394</v>
+        <v>12.85522627830505</v>
       </c>
       <c r="J4" t="n">
-        <v>11.43091940879822</v>
+        <v>13.00684905052185</v>
       </c>
       <c r="K4" t="n">
-        <v>13.35698986053467</v>
+        <v>13.1838972568512</v>
       </c>
       <c r="L4" t="n">
-        <v>12.79742608070373</v>
+        <v>13.08021440505981</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>10.88926315307617</v>
+        <v>10.96456003189087</v>
       </c>
       <c r="C5" t="n">
-        <v>10.96807193756104</v>
+        <v>11.60337162017822</v>
       </c>
       <c r="D5" t="n">
-        <v>10.58856081962585</v>
+        <v>10.78939032554626</v>
       </c>
       <c r="E5" t="n">
-        <v>10.81647109985352</v>
+        <v>10.46924304962158</v>
       </c>
       <c r="F5" t="n">
-        <v>10.02646446228027</v>
+        <v>13.52637243270874</v>
       </c>
       <c r="G5" t="n">
-        <v>10.86389470100403</v>
+        <v>12.50950694084167</v>
       </c>
       <c r="H5" t="n">
-        <v>10.8204550743103</v>
+        <v>11.52947759628296</v>
       </c>
       <c r="I5" t="n">
-        <v>10.96456694602966</v>
+        <v>10.66227650642395</v>
       </c>
       <c r="J5" t="n">
-        <v>12.01142358779907</v>
+        <v>13.0231020450592</v>
       </c>
       <c r="K5" t="n">
-        <v>10.94507169723511</v>
+        <v>11.78533482551575</v>
       </c>
       <c r="L5" t="n">
-        <v>10.8894243478775</v>
+        <v>11.68626353740692</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>13.90835618972778</v>
+        <v>12.82961106300354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.09903264045715</v>
+        <v>12.16682958602905</v>
       </c>
       <c r="D6" t="n">
-        <v>11.06823563575745</v>
+        <v>12.88201689720154</v>
       </c>
       <c r="E6" t="n">
-        <v>11.33802533149719</v>
+        <v>12.89641737937927</v>
       </c>
       <c r="F6" t="n">
-        <v>11.72903370857239</v>
+        <v>13.206622838974</v>
       </c>
       <c r="G6" t="n">
-        <v>13.01716685295105</v>
+        <v>12.16699576377869</v>
       </c>
       <c r="H6" t="n">
-        <v>10.24834632873535</v>
+        <v>12.08417868614197</v>
       </c>
       <c r="I6" t="n">
-        <v>12.33645725250244</v>
+        <v>13.70014691352844</v>
       </c>
       <c r="J6" t="n">
-        <v>10.40094137191772</v>
+        <v>11.33561849594116</v>
       </c>
       <c r="K6" t="n">
-        <v>12.53390431404114</v>
+        <v>13.91303038597107</v>
       </c>
       <c r="L6" t="n">
-        <v>11.86794996261597</v>
+        <v>12.71814680099487</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49959421157837</v>
+        <v>12.45024132728577</v>
       </c>
       <c r="C7" t="n">
-        <v>10.85874891281128</v>
+        <v>11.61739826202393</v>
       </c>
       <c r="D7" t="n">
-        <v>11.60763239860535</v>
+        <v>12.42335510253906</v>
       </c>
       <c r="E7" t="n">
-        <v>10.90574979782104</v>
+        <v>12.33407354354858</v>
       </c>
       <c r="F7" t="n">
-        <v>11.20845031738281</v>
+        <v>12.63681077957153</v>
       </c>
       <c r="G7" t="n">
-        <v>11.30221271514893</v>
+        <v>14.36688804626465</v>
       </c>
       <c r="H7" t="n">
-        <v>10.97515153884888</v>
+        <v>11.36065268516541</v>
       </c>
       <c r="I7" t="n">
-        <v>11.38748979568481</v>
+        <v>12.60136532783508</v>
       </c>
       <c r="J7" t="n">
-        <v>11.34713172912598</v>
+        <v>14.27512168884277</v>
       </c>
       <c r="K7" t="n">
-        <v>11.03291988372803</v>
+        <v>15.19473671913147</v>
       </c>
       <c r="L7" t="n">
-        <v>11.21250813007355</v>
+        <v>12.92606434822082</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09573864936829</v>
+        <v>12.25212407112122</v>
       </c>
       <c r="C8" t="n">
-        <v>11.9582211971283</v>
+        <v>12.74934148788452</v>
       </c>
       <c r="D8" t="n">
-        <v>13.42150235176086</v>
+        <v>13.16666030883789</v>
       </c>
       <c r="E8" t="n">
-        <v>11.00151753425598</v>
+        <v>12.40693211555481</v>
       </c>
       <c r="F8" t="n">
-        <v>11.29873442649841</v>
+        <v>11.37045741081238</v>
       </c>
       <c r="G8" t="n">
-        <v>11.54708743095398</v>
+        <v>11.49757122993469</v>
       </c>
       <c r="H8" t="n">
-        <v>11.27577781677246</v>
+        <v>12.30000734329224</v>
       </c>
       <c r="I8" t="n">
-        <v>10.9905264377594</v>
+        <v>11.90153956413269</v>
       </c>
       <c r="J8" t="n">
-        <v>11.66584062576294</v>
+        <v>12.78375458717346</v>
       </c>
       <c r="K8" t="n">
-        <v>10.66085076332092</v>
+        <v>11.76388382911682</v>
       </c>
       <c r="L8" t="n">
-        <v>11.49157972335815</v>
+        <v>12.21922719478607</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>10.72523617744446</v>
+        <v>12.84555292129517</v>
       </c>
       <c r="C9" t="n">
-        <v>10.80546379089355</v>
+        <v>11.94091558456421</v>
       </c>
       <c r="D9" t="n">
-        <v>11.49827265739441</v>
+        <v>12.10650086402893</v>
       </c>
       <c r="E9" t="n">
-        <v>11.77760767936707</v>
+        <v>11.79233479499817</v>
       </c>
       <c r="F9" t="n">
-        <v>13.01085805892944</v>
+        <v>13.79211258888245</v>
       </c>
       <c r="G9" t="n">
-        <v>10.93466329574585</v>
+        <v>11.93344497680664</v>
       </c>
       <c r="H9" t="n">
-        <v>13.02182769775391</v>
+        <v>11.33404874801636</v>
       </c>
       <c r="I9" t="n">
-        <v>10.89875102043152</v>
+        <v>11.49711084365845</v>
       </c>
       <c r="J9" t="n">
-        <v>11.0399329662323</v>
+        <v>13.14353275299072</v>
       </c>
       <c r="K9" t="n">
-        <v>10.85936999320984</v>
+        <v>11.3694896697998</v>
       </c>
       <c r="L9" t="n">
-        <v>11.45719833374023</v>
+        <v>12.17550437450409</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>11.95657634735107</v>
+        <v>11.70866203308105</v>
       </c>
       <c r="C10" t="n">
-        <v>12.13459753990173</v>
+        <v>15.62353706359863</v>
       </c>
       <c r="D10" t="n">
-        <v>12.23085737228394</v>
+        <v>15.33645939826965</v>
       </c>
       <c r="E10" t="n">
-        <v>10.36507272720337</v>
+        <v>12.44430017471313</v>
       </c>
       <c r="F10" t="n">
-        <v>13.24429082870483</v>
+        <v>11.19547963142395</v>
       </c>
       <c r="G10" t="n">
-        <v>11.09029459953308</v>
+        <v>12.4472553730011</v>
       </c>
       <c r="H10" t="n">
-        <v>11.73859524726868</v>
+        <v>11.55665063858032</v>
       </c>
       <c r="I10" t="n">
-        <v>11.05289196968079</v>
+        <v>11.31465196609497</v>
       </c>
       <c r="J10" t="n">
-        <v>14.30208301544189</v>
+        <v>12.31117296218872</v>
       </c>
       <c r="K10" t="n">
-        <v>15.07884979248047</v>
+        <v>12.01582551002502</v>
       </c>
       <c r="L10" t="n">
-        <v>12.31941094398499</v>
+        <v>12.59539947509766</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>11.95303630828857</v>
+        <v>15.08921933174133</v>
       </c>
       <c r="C11" t="n">
-        <v>11.88824009895325</v>
+        <v>12.65606093406677</v>
       </c>
       <c r="D11" t="n">
-        <v>10.98651504516602</v>
+        <v>13.20861744880676</v>
       </c>
       <c r="E11" t="n">
-        <v>11.57955646514893</v>
+        <v>12.25113582611084</v>
       </c>
       <c r="F11" t="n">
-        <v>12.19844102859497</v>
+        <v>12.71042013168335</v>
       </c>
       <c r="G11" t="n">
-        <v>11.05237793922424</v>
+        <v>12.48848485946655</v>
       </c>
       <c r="H11" t="n">
-        <v>10.84734797477722</v>
+        <v>12.97721672058105</v>
       </c>
       <c r="I11" t="n">
-        <v>11.55210113525391</v>
+        <v>11.70105886459351</v>
       </c>
       <c r="J11" t="n">
-        <v>11.54509997367859</v>
+        <v>12.86055636405945</v>
       </c>
       <c r="K11" t="n">
-        <v>11.76307106018066</v>
+        <v>11.58438372612</v>
       </c>
       <c r="L11" t="n">
-        <v>11.53657870292664</v>
+        <v>12.75271542072296</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>11.83189845085144</v>
+        <v>12.28103733062744</v>
       </c>
       <c r="C12" t="n">
-        <v>11.66926026344299</v>
+        <v>14.03092932701111</v>
       </c>
       <c r="D12" t="n">
-        <v>18.69699716567993</v>
+        <v>12.9981689453125</v>
       </c>
       <c r="E12" t="n">
-        <v>18.24179339408875</v>
+        <v>12.33839559555054</v>
       </c>
       <c r="F12" t="n">
-        <v>12.17652034759521</v>
+        <v>12.0870475769043</v>
       </c>
       <c r="G12" t="n">
-        <v>13.01886940002441</v>
+        <v>16.55681133270264</v>
       </c>
       <c r="H12" t="n">
-        <v>12.4997227191925</v>
+        <v>13.05205106735229</v>
       </c>
       <c r="I12" t="n">
-        <v>13.32956004142761</v>
+        <v>12.29944729804993</v>
       </c>
       <c r="J12" t="n">
-        <v>13.96790885925293</v>
+        <v>13.43971753120422</v>
       </c>
       <c r="K12" t="n">
-        <v>10.97257447242737</v>
+        <v>12.75299739837646</v>
       </c>
       <c r="L12" t="n">
-        <v>13.64051051139831</v>
+        <v>13.18366034030914</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>12.5395724773407</v>
+        <v>13.08019256591797</v>
       </c>
       <c r="C13" t="n">
-        <v>12.29776883125305</v>
+        <v>13.96593689918518</v>
       </c>
       <c r="D13" t="n">
-        <v>14.27843070030212</v>
+        <v>14.71199035644531</v>
       </c>
       <c r="E13" t="n">
-        <v>12.99171662330627</v>
+        <v>13.03575468063354</v>
       </c>
       <c r="F13" t="n">
-        <v>12.7508716583252</v>
+        <v>13.28217363357544</v>
       </c>
       <c r="G13" t="n">
-        <v>12.52492833137512</v>
+        <v>15.27356028556824</v>
       </c>
       <c r="H13" t="n">
-        <v>11.50410509109497</v>
+        <v>12.12518191337585</v>
       </c>
       <c r="I13" t="n">
-        <v>12.13797068595886</v>
+        <v>13.2951123714447</v>
       </c>
       <c r="J13" t="n">
-        <v>12.19330525398254</v>
+        <v>13.31258296966553</v>
       </c>
       <c r="K13" t="n">
-        <v>12.66009044647217</v>
+        <v>14.3618757724762</v>
       </c>
       <c r="L13" t="n">
-        <v>12.5878760099411</v>
+        <v>13.6444361448288</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>12.69499397277832</v>
+        <v>13.75545287132263</v>
       </c>
       <c r="C14" t="n">
-        <v>15.86274194717407</v>
+        <v>12.4692497253418</v>
       </c>
       <c r="D14" t="n">
-        <v>12.32644438743591</v>
+        <v>13.06429743766785</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1560275554657</v>
+        <v>12.53954386711121</v>
       </c>
       <c r="F14" t="n">
-        <v>11.91255688667297</v>
+        <v>16.04312419891357</v>
       </c>
       <c r="G14" t="n">
-        <v>11.36080527305603</v>
+        <v>12.61383438110352</v>
       </c>
       <c r="H14" t="n">
-        <v>11.60949230194092</v>
+        <v>16.37775325775146</v>
       </c>
       <c r="I14" t="n">
-        <v>12.02145957946777</v>
+        <v>12.86722302436829</v>
       </c>
       <c r="J14" t="n">
-        <v>11.0428774356842</v>
+        <v>12.5355966091156</v>
       </c>
       <c r="K14" t="n">
-        <v>17.2241735458374</v>
+        <v>18.96113014221191</v>
       </c>
       <c r="L14" t="n">
-        <v>12.72115728855133</v>
+        <v>14.12272055149078</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>10.68681406974792</v>
+        <v>12.21187591552734</v>
       </c>
       <c r="C15" t="n">
-        <v>12.42935252189636</v>
+        <v>12.17575526237488</v>
       </c>
       <c r="D15" t="n">
-        <v>11.55964708328247</v>
+        <v>11.37604737281799</v>
       </c>
       <c r="E15" t="n">
-        <v>13.61182737350464</v>
+        <v>15.18684220314026</v>
       </c>
       <c r="F15" t="n">
-        <v>13.63331294059753</v>
+        <v>12.14253187179565</v>
       </c>
       <c r="G15" t="n">
-        <v>10.93414282798767</v>
+        <v>13.26868486404419</v>
       </c>
       <c r="H15" t="n">
-        <v>11.93812131881714</v>
+        <v>15.02718591690063</v>
       </c>
       <c r="I15" t="n">
-        <v>11.06381225585938</v>
+        <v>13.13952231407166</v>
       </c>
       <c r="J15" t="n">
-        <v>13.85674095153809</v>
+        <v>12.14455223083496</v>
       </c>
       <c r="K15" t="n">
-        <v>11.37403035163879</v>
+        <v>12.03446006774902</v>
       </c>
       <c r="L15" t="n">
-        <v>12.108780169487</v>
+        <v>12.87074580192566</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>12.18694615364075</v>
+        <v>12.35132718086243</v>
       </c>
       <c r="C16" t="n">
-        <v>12.04136252403259</v>
+        <v>17.88697671890259</v>
       </c>
       <c r="D16" t="n">
-        <v>12.35005593299866</v>
+        <v>13.28245234489441</v>
       </c>
       <c r="E16" t="n">
-        <v>12.14952373504639</v>
+        <v>15.30268335342407</v>
       </c>
       <c r="F16" t="n">
-        <v>11.40362477302551</v>
+        <v>13.19967365264893</v>
       </c>
       <c r="G16" t="n">
-        <v>16.53934717178345</v>
+        <v>12.53587102890015</v>
       </c>
       <c r="H16" t="n">
-        <v>12.91460943222046</v>
+        <v>12.90041470527649</v>
       </c>
       <c r="I16" t="n">
-        <v>13.12412452697754</v>
+        <v>11.92743110656738</v>
       </c>
       <c r="J16" t="n">
-        <v>14.40377998352051</v>
+        <v>12.29655599594116</v>
       </c>
       <c r="K16" t="n">
-        <v>11.82788443565369</v>
+        <v>11.83619379997253</v>
       </c>
       <c r="L16" t="n">
-        <v>12.89412586688995</v>
+        <v>13.35195798873901</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>11.3521089553833</v>
+        <v>12.39522528648376</v>
       </c>
       <c r="C17" t="n">
-        <v>10.91571092605591</v>
+        <v>17.61292195320129</v>
       </c>
       <c r="D17" t="n">
-        <v>11.62342143058777</v>
+        <v>14.65305018424988</v>
       </c>
       <c r="E17" t="n">
-        <v>10.82392406463623</v>
+        <v>16.7273485660553</v>
       </c>
       <c r="F17" t="n">
-        <v>11.05633950233459</v>
+        <v>15.39200472831726</v>
       </c>
       <c r="G17" t="n">
-        <v>11.57604598999023</v>
+        <v>14.4412305355072</v>
       </c>
       <c r="H17" t="n">
-        <v>17.86153483390808</v>
+        <v>13.77984142303467</v>
       </c>
       <c r="I17" t="n">
-        <v>10.59701490402222</v>
+        <v>11.87103724479675</v>
       </c>
       <c r="J17" t="n">
-        <v>11.17854881286621</v>
+        <v>12.00699782371521</v>
       </c>
       <c r="K17" t="n">
-        <v>13.01277947425842</v>
+        <v>16.44390201568604</v>
       </c>
       <c r="L17" t="n">
-        <v>11.9997428894043</v>
+        <v>14.53235597610474</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>14.71473217010498</v>
+        <v>15.91463947296143</v>
       </c>
       <c r="C18" t="n">
-        <v>15.03090834617615</v>
+        <v>18.13262605667114</v>
       </c>
       <c r="D18" t="n">
-        <v>12.34512424468994</v>
+        <v>14.61554026603699</v>
       </c>
       <c r="E18" t="n">
-        <v>13.15102434158325</v>
+        <v>15.13471055030823</v>
       </c>
       <c r="F18" t="n">
-        <v>14.52400660514832</v>
+        <v>14.40542602539062</v>
       </c>
       <c r="G18" t="n">
-        <v>14.35744547843933</v>
+        <v>12.47396516799927</v>
       </c>
       <c r="H18" t="n">
-        <v>14.10306715965271</v>
+        <v>11.57571053504944</v>
       </c>
       <c r="I18" t="n">
-        <v>13.28763818740845</v>
+        <v>16.02539110183716</v>
       </c>
       <c r="J18" t="n">
-        <v>14.1414532661438</v>
+        <v>13.22167658805847</v>
       </c>
       <c r="K18" t="n">
-        <v>14.75493454933167</v>
+        <v>13.02990865707397</v>
       </c>
       <c r="L18" t="n">
-        <v>14.04103343486786</v>
+        <v>14.45295944213867</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>11.48923444747925</v>
+        <v>12.82361149787903</v>
       </c>
       <c r="C19" t="n">
-        <v>11.47926712036133</v>
+        <v>14.41259384155273</v>
       </c>
       <c r="D19" t="n">
-        <v>12.02023935317993</v>
+        <v>13.99367213249207</v>
       </c>
       <c r="E19" t="n">
-        <v>11.3280553817749</v>
+        <v>13.77064514160156</v>
       </c>
       <c r="F19" t="n">
-        <v>13.3302161693573</v>
+        <v>14.84829711914062</v>
       </c>
       <c r="G19" t="n">
-        <v>13.21677803993225</v>
+        <v>13.24583292007446</v>
       </c>
       <c r="H19" t="n">
-        <v>12.42571091651917</v>
+        <v>17.84700512886047</v>
       </c>
       <c r="I19" t="n">
-        <v>14.26744508743286</v>
+        <v>12.05413341522217</v>
       </c>
       <c r="J19" t="n">
-        <v>11.05529427528381</v>
+        <v>13.35282778739929</v>
       </c>
       <c r="K19" t="n">
-        <v>14.28190207481384</v>
+        <v>13.18734312057495</v>
       </c>
       <c r="L19" t="n">
-        <v>12.48941428661346</v>
+        <v>13.95359621047974</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>14.0788688659668</v>
+        <v>13.3853759765625</v>
       </c>
       <c r="C20" t="n">
-        <v>10.60540080070496</v>
+        <v>10.68169283866882</v>
       </c>
       <c r="D20" t="n">
-        <v>10.97001028060913</v>
+        <v>12.83184480667114</v>
       </c>
       <c r="E20" t="n">
-        <v>10.72458791732788</v>
+        <v>13.12009501457214</v>
       </c>
       <c r="F20" t="n">
-        <v>10.34698176383972</v>
+        <v>16.87542271614075</v>
       </c>
       <c r="G20" t="n">
-        <v>10.6853129863739</v>
+        <v>15.24232578277588</v>
       </c>
       <c r="H20" t="n">
-        <v>9.592561006546021</v>
+        <v>11.76381373405457</v>
       </c>
       <c r="I20" t="n">
-        <v>11.69413352012634</v>
+        <v>12.51282238960266</v>
       </c>
       <c r="J20" t="n">
-        <v>15.13094544410706</v>
+        <v>11.1611168384552</v>
       </c>
       <c r="K20" t="n">
-        <v>10.94163513183594</v>
+        <v>11.13847708702087</v>
       </c>
       <c r="L20" t="n">
-        <v>11.47704377174377</v>
+        <v>12.87129871845245</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>11.30619549751282</v>
+        <v>11.92143559455872</v>
       </c>
       <c r="C21" t="n">
-        <v>11.23139452934265</v>
+        <v>12.88570761680603</v>
       </c>
       <c r="D21" t="n">
-        <v>10.66139149665833</v>
+        <v>12.76061129570007</v>
       </c>
       <c r="E21" t="n">
-        <v>11.15608930587769</v>
+        <v>11.87139225006104</v>
       </c>
       <c r="F21" t="n">
-        <v>10.92667198181152</v>
+        <v>12.93041276931763</v>
       </c>
       <c r="G21" t="n">
-        <v>11.40398669242859</v>
+        <v>12.82490992546082</v>
       </c>
       <c r="H21" t="n">
-        <v>10.83738684654236</v>
+        <v>12.22759962081909</v>
       </c>
       <c r="I21" t="n">
-        <v>11.52514696121216</v>
+        <v>14.57189154624939</v>
       </c>
       <c r="J21" t="n">
-        <v>10.93862891197205</v>
+        <v>13.10309314727783</v>
       </c>
       <c r="K21" t="n">
-        <v>11.20152616500854</v>
+        <v>13.74129891395569</v>
       </c>
       <c r="L21" t="n">
-        <v>11.11884183883667</v>
+        <v>12.88383526802063</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>13.69411587715149</v>
+        <v>13.76374101638794</v>
       </c>
       <c r="C22" t="n">
-        <v>11.48225951194763</v>
+        <v>12.86483883857727</v>
       </c>
       <c r="D22" t="n">
-        <v>12.426344871521</v>
+        <v>13.80859875679016</v>
       </c>
       <c r="E22" t="n">
-        <v>11.91920614242554</v>
+        <v>15.23486661911011</v>
       </c>
       <c r="F22" t="n">
-        <v>13.13007020950317</v>
+        <v>13.37105560302734</v>
       </c>
       <c r="G22" t="n">
-        <v>11.44888734817505</v>
+        <v>16.85561347007751</v>
       </c>
       <c r="H22" t="n">
-        <v>11.96504068374634</v>
+        <v>13.15436124801636</v>
       </c>
       <c r="I22" t="n">
-        <v>11.3630805015564</v>
+        <v>16.70457029342651</v>
       </c>
       <c r="J22" t="n">
-        <v>12.53962659835815</v>
+        <v>17.24398946762085</v>
       </c>
       <c r="K22" t="n">
-        <v>12.15856170654297</v>
+        <v>20.63846683502197</v>
       </c>
       <c r="L22" t="n">
-        <v>12.21271934509277</v>
+        <v>15.3640102148056</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.50878834724426</v>
+        <v>14.21581816673279</v>
       </c>
       <c r="C23" t="n">
-        <v>13.59836864471436</v>
+        <v>17.33539080619812</v>
       </c>
       <c r="D23" t="n">
-        <v>10.54861164093018</v>
+        <v>17.75892639160156</v>
       </c>
       <c r="E23" t="n">
-        <v>10.60700917243958</v>
+        <v>16.19673848152161</v>
       </c>
       <c r="F23" t="n">
-        <v>11.40890312194824</v>
+        <v>10.99090528488159</v>
       </c>
       <c r="G23" t="n">
-        <v>10.91820597648621</v>
+        <v>14.32825946807861</v>
       </c>
       <c r="H23" t="n">
-        <v>11.78001093864441</v>
+        <v>11.92944645881653</v>
       </c>
       <c r="I23" t="n">
-        <v>11.20447254180908</v>
+        <v>13.12534284591675</v>
       </c>
       <c r="J23" t="n">
-        <v>11.41892099380493</v>
+        <v>12.55232453346252</v>
       </c>
       <c r="K23" t="n">
-        <v>11.46877980232239</v>
+        <v>11.01089143753052</v>
       </c>
       <c r="L23" t="n">
-        <v>11.34620711803436</v>
+        <v>13.94440438747406</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>12.44733786582947</v>
+        <v>12.6460645198822</v>
       </c>
       <c r="C24" t="n">
-        <v>11.7600531578064</v>
+        <v>15.38332056999207</v>
       </c>
       <c r="D24" t="n">
-        <v>15.32047772407532</v>
+        <v>18.25028681755066</v>
       </c>
       <c r="E24" t="n">
-        <v>11.55806756019592</v>
+        <v>18.09057712554932</v>
       </c>
       <c r="F24" t="n">
-        <v>12.20097875595093</v>
+        <v>13.94586563110352</v>
       </c>
       <c r="G24" t="n">
-        <v>12.26282048225403</v>
+        <v>12.69747471809387</v>
       </c>
       <c r="H24" t="n">
-        <v>11.15508055686951</v>
+        <v>14.34163069725037</v>
       </c>
       <c r="I24" t="n">
-        <v>11.70969557762146</v>
+        <v>14.01891207695007</v>
       </c>
       <c r="J24" t="n">
-        <v>12.35508275032043</v>
+        <v>18.35197186470032</v>
       </c>
       <c r="K24" t="n">
-        <v>11.5311131477356</v>
+        <v>12.78119945526123</v>
       </c>
       <c r="L24" t="n">
-        <v>12.23007075786591</v>
+        <v>15.05073034763336</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>12.88973045349121</v>
+        <v>15.27141451835632</v>
       </c>
       <c r="C25" t="n">
-        <v>13.43179512023926</v>
+        <v>16.87305045127869</v>
       </c>
       <c r="D25" t="n">
-        <v>13.97390484809875</v>
+        <v>15.29054856300354</v>
       </c>
       <c r="E25" t="n">
-        <v>12.96599149703979</v>
+        <v>14.33360862731934</v>
       </c>
       <c r="F25" t="n">
-        <v>13.11316561698914</v>
+        <v>15.46548080444336</v>
       </c>
       <c r="G25" t="n">
-        <v>13.42375087738037</v>
+        <v>15.00872993469238</v>
       </c>
       <c r="H25" t="n">
-        <v>12.90442442893982</v>
+        <v>17.63332271575928</v>
       </c>
       <c r="I25" t="n">
-        <v>16.21583437919617</v>
+        <v>16.10744047164917</v>
       </c>
       <c r="J25" t="n">
-        <v>16.20284414291382</v>
+        <v>17.68898344039917</v>
       </c>
       <c r="K25" t="n">
-        <v>13.39767599105835</v>
+        <v>14.48003077507019</v>
       </c>
       <c r="L25" t="n">
-        <v>13.85191173553467</v>
+        <v>15.81526103019714</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>13.50936508178711</v>
+        <v>11.33597040176392</v>
       </c>
       <c r="C26" t="n">
-        <v>10.14762806892395</v>
+        <v>11.75639939308167</v>
       </c>
       <c r="D26" t="n">
-        <v>10.52366137504578</v>
+        <v>14.61287665367126</v>
       </c>
       <c r="E26" t="n">
-        <v>9.824462175369263</v>
+        <v>13.38329768180847</v>
       </c>
       <c r="F26" t="n">
-        <v>10.3341543674469</v>
+        <v>17.39964723587036</v>
       </c>
       <c r="G26" t="n">
-        <v>10.2393970489502</v>
+        <v>12.68565082550049</v>
       </c>
       <c r="H26" t="n">
-        <v>10.69121313095093</v>
+        <v>13.46477675437927</v>
       </c>
       <c r="I26" t="n">
-        <v>10.92911219596863</v>
+        <v>12.50918650627136</v>
       </c>
       <c r="J26" t="n">
-        <v>10.16652417182922</v>
+        <v>12.01330399513245</v>
       </c>
       <c r="K26" t="n">
-        <v>11.30211043357849</v>
+        <v>11.24874567985535</v>
       </c>
       <c r="L26" t="n">
-        <v>10.76676280498505</v>
+        <v>13.04098551273346</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>11.82029461860657</v>
+        <v>16.14190864562988</v>
       </c>
       <c r="C27" t="n">
-        <v>12.22964882850647</v>
+        <v>11.29188585281372</v>
       </c>
       <c r="D27" t="n">
-        <v>16.07005596160889</v>
+        <v>16.58416247367859</v>
       </c>
       <c r="E27" t="n">
-        <v>13.4228458404541</v>
+        <v>18.21238565444946</v>
       </c>
       <c r="F27" t="n">
-        <v>11.58850336074829</v>
+        <v>12.40912294387817</v>
       </c>
       <c r="G27" t="n">
-        <v>16.18230175971985</v>
+        <v>12.69394040107727</v>
       </c>
       <c r="H27" t="n">
-        <v>15.48156762123108</v>
+        <v>12.63082146644592</v>
       </c>
       <c r="I27" t="n">
-        <v>11.23537874221802</v>
+        <v>12.07749271392822</v>
       </c>
       <c r="J27" t="n">
-        <v>16.39827466011047</v>
+        <v>13.11571741104126</v>
       </c>
       <c r="K27" t="n">
-        <v>12.43033075332642</v>
+        <v>14.84299302101135</v>
       </c>
       <c r="L27" t="n">
-        <v>13.68592021465301</v>
+        <v>14.00004305839539</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>11.30172228813171</v>
+        <v>11.41193032264709</v>
       </c>
       <c r="C28" t="n">
-        <v>11.18156909942627</v>
+        <v>11.69495964050293</v>
       </c>
       <c r="D28" t="n">
-        <v>14.41778111457825</v>
+        <v>12.063148021698</v>
       </c>
       <c r="E28" t="n">
-        <v>11.07834792137146</v>
+        <v>11.57917833328247</v>
       </c>
       <c r="F28" t="n">
-        <v>11.72363090515137</v>
+        <v>11.91304230690002</v>
       </c>
       <c r="G28" t="n">
-        <v>10.74313068389893</v>
+        <v>11.38110113143921</v>
       </c>
       <c r="H28" t="n">
-        <v>12.54757595062256</v>
+        <v>11.34532904624939</v>
       </c>
       <c r="I28" t="n">
-        <v>11.37404990196228</v>
+        <v>10.74688458442688</v>
       </c>
       <c r="J28" t="n">
-        <v>10.63096690177917</v>
+        <v>11.87976312637329</v>
       </c>
       <c r="K28" t="n">
-        <v>13.2754499912262</v>
+        <v>11.93556380271912</v>
       </c>
       <c r="L28" t="n">
-        <v>11.82742247581482</v>
+        <v>11.59509003162384</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>10.35164022445679</v>
+        <v>11.25742602348328</v>
       </c>
       <c r="C29" t="n">
-        <v>10.58945631980896</v>
+        <v>11.42703866958618</v>
       </c>
       <c r="D29" t="n">
-        <v>10.15109515190125</v>
+        <v>12.09247136116028</v>
       </c>
       <c r="E29" t="n">
-        <v>10.30270266532898</v>
+        <v>11.11301374435425</v>
       </c>
       <c r="F29" t="n">
-        <v>9.801533460617065</v>
+        <v>10.74304699897766</v>
       </c>
       <c r="G29" t="n">
-        <v>13.14532804489136</v>
+        <v>12.04817914962769</v>
       </c>
       <c r="H29" t="n">
-        <v>9.797924995422363</v>
+        <v>10.0746922492981</v>
       </c>
       <c r="I29" t="n">
-        <v>10.68177437782288</v>
+        <v>11.51615405082703</v>
       </c>
       <c r="J29" t="n">
-        <v>10.25141596794128</v>
+        <v>11.57100796699524</v>
       </c>
       <c r="K29" t="n">
-        <v>10.89722871780396</v>
+        <v>10.03858065605164</v>
       </c>
       <c r="L29" t="n">
-        <v>10.59700999259949</v>
+        <v>11.18816108703613</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>12.6253604888916</v>
+        <v>12.55351161956787</v>
       </c>
       <c r="C30" t="n">
-        <v>14.91248893737793</v>
+        <v>11.8836727142334</v>
       </c>
       <c r="D30" t="n">
-        <v>11.42398023605347</v>
+        <v>11.86297202110291</v>
       </c>
       <c r="E30" t="n">
-        <v>10.60704517364502</v>
+        <v>11.40212035179138</v>
       </c>
       <c r="F30" t="n">
-        <v>10.92971777915955</v>
+        <v>12.30483460426331</v>
       </c>
       <c r="G30" t="n">
-        <v>16.23112177848816</v>
+        <v>11.70568108558655</v>
       </c>
       <c r="H30" t="n">
-        <v>11.72901892662048</v>
+        <v>11.25379276275635</v>
       </c>
       <c r="I30" t="n">
-        <v>10.42887163162231</v>
+        <v>11.71218943595886</v>
       </c>
       <c r="J30" t="n">
-        <v>10.59745979309082</v>
+        <v>14.79697465896606</v>
       </c>
       <c r="K30" t="n">
-        <v>11.68464684486389</v>
+        <v>15.28884077072144</v>
       </c>
       <c r="L30" t="n">
-        <v>12.11697115898132</v>
+        <v>12.47645900249481</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>11.72461152076721</v>
+        <v>14.25899744033813</v>
       </c>
       <c r="C31" t="n">
-        <v>11.29871034622192</v>
+        <v>16.87287330627441</v>
       </c>
       <c r="D31" t="n">
-        <v>11.31271409988403</v>
+        <v>16.23254203796387</v>
       </c>
       <c r="E31" t="n">
-        <v>13.78989267349243</v>
+        <v>12.56028461456299</v>
       </c>
       <c r="F31" t="n">
-        <v>12.46726560592651</v>
+        <v>13.65529823303223</v>
       </c>
       <c r="G31" t="n">
-        <v>11.80497193336487</v>
+        <v>13.84230208396912</v>
       </c>
       <c r="H31" t="n">
-        <v>13.80930089950562</v>
+        <v>13.94704008102417</v>
       </c>
       <c r="I31" t="n">
-        <v>12.93857359886169</v>
+        <v>11.37617969512939</v>
       </c>
       <c r="J31" t="n">
-        <v>16.19077563285828</v>
+        <v>11.06564784049988</v>
       </c>
       <c r="K31" t="n">
-        <v>14.62480878829956</v>
+        <v>11.48797607421875</v>
       </c>
       <c r="L31" t="n">
-        <v>12.99616250991821</v>
+        <v>13.52991414070129</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>10.81346821784973</v>
+        <v>11.54946088790894</v>
       </c>
       <c r="C32" t="n">
-        <v>11.23740744590759</v>
+        <v>12.24426627159119</v>
       </c>
       <c r="D32" t="n">
-        <v>13.09419965744019</v>
+        <v>15.24098515510559</v>
       </c>
       <c r="E32" t="n">
-        <v>11.9859893321991</v>
+        <v>13.4635157585144</v>
       </c>
       <c r="F32" t="n">
-        <v>12.88174724578857</v>
+        <v>11.22471523284912</v>
       </c>
       <c r="G32" t="n">
-        <v>14.53549218177795</v>
+        <v>11.37188911437988</v>
       </c>
       <c r="H32" t="n">
-        <v>12.14957094192505</v>
+        <v>14.67446899414062</v>
       </c>
       <c r="I32" t="n">
-        <v>11.03690314292908</v>
+        <v>11.71921157836914</v>
       </c>
       <c r="J32" t="n">
-        <v>14.34005308151245</v>
+        <v>11.14597153663635</v>
       </c>
       <c r="K32" t="n">
-        <v>11.36811065673828</v>
+        <v>11.88459491729736</v>
       </c>
       <c r="L32" t="n">
-        <v>12.3442941904068</v>
+        <v>12.45190794467926</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>13.350013256073</v>
+        <v>12.17202639579773</v>
       </c>
       <c r="C33" t="n">
-        <v>11.51753854751587</v>
+        <v>11.92190504074097</v>
       </c>
       <c r="D33" t="n">
-        <v>11.63571834564209</v>
+        <v>11.6235830783844</v>
       </c>
       <c r="E33" t="n">
-        <v>11.69611167907715</v>
+        <v>12.35093927383423</v>
       </c>
       <c r="F33" t="n">
-        <v>12.21073603630066</v>
+        <v>12.56544971466064</v>
       </c>
       <c r="G33" t="n">
-        <v>11.92453193664551</v>
+        <v>12.17115497589111</v>
       </c>
       <c r="H33" t="n">
-        <v>11.67017698287964</v>
+        <v>13.48691868782043</v>
       </c>
       <c r="I33" t="n">
-        <v>11.83751082420349</v>
+        <v>12.11888980865479</v>
       </c>
       <c r="J33" t="n">
-        <v>12.85429525375366</v>
+        <v>13.41816306114197</v>
       </c>
       <c r="K33" t="n">
-        <v>11.28678441047668</v>
+        <v>14.58425879478455</v>
       </c>
       <c r="L33" t="n">
-        <v>11.99834172725678</v>
+        <v>12.64132888317108</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>11.63038349151611</v>
+        <v>12.07986879348755</v>
       </c>
       <c r="C34" t="n">
-        <v>10.43446087837219</v>
+        <v>12.98706912994385</v>
       </c>
       <c r="D34" t="n">
-        <v>10.797518491745</v>
+        <v>11.56894516944885</v>
       </c>
       <c r="E34" t="n">
-        <v>10.71724820137024</v>
+        <v>10.47315263748169</v>
       </c>
       <c r="F34" t="n">
-        <v>12.62485718727112</v>
+        <v>12.7433774471283</v>
       </c>
       <c r="G34" t="n">
-        <v>10.53108358383179</v>
+        <v>10.45658373832703</v>
       </c>
       <c r="H34" t="n">
-        <v>11.50462293624878</v>
+        <v>11.05952930450439</v>
       </c>
       <c r="I34" t="n">
-        <v>11.53449845314026</v>
+        <v>11.35435152053833</v>
       </c>
       <c r="J34" t="n">
-        <v>10.88170313835144</v>
+        <v>11.33474636077881</v>
       </c>
       <c r="K34" t="n">
-        <v>10.93409490585327</v>
+        <v>12.51302766799927</v>
       </c>
       <c r="L34" t="n">
-        <v>11.15904712677002</v>
+        <v>11.65706517696381</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>11.84922742843628</v>
+        <v>13.41191458702087</v>
       </c>
       <c r="C35" t="n">
-        <v>10.91167044639587</v>
+        <v>11.80943870544434</v>
       </c>
       <c r="D35" t="n">
-        <v>11.65433311462402</v>
+        <v>12.40426182746887</v>
       </c>
       <c r="E35" t="n">
-        <v>11.46976637840271</v>
+        <v>16.21025037765503</v>
       </c>
       <c r="F35" t="n">
-        <v>11.87393450737</v>
+        <v>17.95812821388245</v>
       </c>
       <c r="G35" t="n">
-        <v>11.51516199111938</v>
+        <v>12.58634543418884</v>
       </c>
       <c r="H35" t="n">
-        <v>11.00645780563354</v>
+        <v>13.64920926094055</v>
       </c>
       <c r="I35" t="n">
-        <v>16.30294013023376</v>
+        <v>12.21093010902405</v>
       </c>
       <c r="J35" t="n">
-        <v>12.43431711196899</v>
+        <v>12.66585636138916</v>
       </c>
       <c r="K35" t="n">
-        <v>11.59648656845093</v>
+        <v>13.05924201011658</v>
       </c>
       <c r="L35" t="n">
-        <v>12.06142954826355</v>
+        <v>13.59655768871307</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>11.49426460266113</v>
+        <v>13.08896398544312</v>
       </c>
       <c r="C36" t="n">
-        <v>11.15611290931702</v>
+        <v>12.42270565032959</v>
       </c>
       <c r="D36" t="n">
-        <v>14.72705912590027</v>
+        <v>12.6588442325592</v>
       </c>
       <c r="E36" t="n">
-        <v>12.81541681289673</v>
+        <v>11.72710752487183</v>
       </c>
       <c r="F36" t="n">
-        <v>11.02192807197571</v>
+        <v>16.68007802963257</v>
       </c>
       <c r="G36" t="n">
-        <v>11.34363532066345</v>
+        <v>14.58158779144287</v>
       </c>
       <c r="H36" t="n">
-        <v>11.52314925193787</v>
+        <v>13.68892192840576</v>
       </c>
       <c r="I36" t="n">
-        <v>11.20252919197083</v>
+        <v>13.1756067276001</v>
       </c>
       <c r="J36" t="n">
-        <v>12.49824476242065</v>
+        <v>12.43961787223816</v>
       </c>
       <c r="K36" t="n">
-        <v>11.41196870803833</v>
+        <v>16.07494354248047</v>
       </c>
       <c r="L36" t="n">
-        <v>11.9194308757782</v>
+        <v>13.65383772850037</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>12.23989677429199</v>
+        <v>13.50735831260681</v>
       </c>
       <c r="C37" t="n">
-        <v>11.86232805252075</v>
+        <v>12.16462731361389</v>
       </c>
       <c r="D37" t="n">
-        <v>11.43993592262268</v>
+        <v>12.49743556976318</v>
       </c>
       <c r="E37" t="n">
-        <v>10.54763150215149</v>
+        <v>12.30933880805969</v>
       </c>
       <c r="F37" t="n">
-        <v>10.71921300888062</v>
+        <v>12.42408561706543</v>
       </c>
       <c r="G37" t="n">
-        <v>11.08234977722168</v>
+        <v>11.77108788490295</v>
       </c>
       <c r="H37" t="n">
-        <v>10.81791520118713</v>
+        <v>13.04056358337402</v>
       </c>
       <c r="I37" t="n">
-        <v>17.14298534393311</v>
+        <v>12.32758784294128</v>
       </c>
       <c r="J37" t="n">
-        <v>11.9201385974884</v>
+        <v>11.7158203125</v>
       </c>
       <c r="K37" t="n">
-        <v>11.42598128318787</v>
+        <v>12.06537842750549</v>
       </c>
       <c r="L37" t="n">
-        <v>11.91983754634857</v>
+        <v>12.38232836723328</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>11.24237561225891</v>
+        <v>11.87389922142029</v>
       </c>
       <c r="C38" t="n">
-        <v>13.82480025291443</v>
+        <v>12.87472605705261</v>
       </c>
       <c r="D38" t="n">
-        <v>11.10323190689087</v>
+        <v>13.20255613327026</v>
       </c>
       <c r="E38" t="n">
-        <v>11.00183439254761</v>
+        <v>12.16207432746887</v>
       </c>
       <c r="F38" t="n">
-        <v>10.40097165107727</v>
+        <v>12.15702843666077</v>
       </c>
       <c r="G38" t="n">
-        <v>10.69767451286316</v>
+        <v>11.95584416389465</v>
       </c>
       <c r="H38" t="n">
-        <v>11.21783399581909</v>
+        <v>16.29820203781128</v>
       </c>
       <c r="I38" t="n">
-        <v>11.77590036392212</v>
+        <v>12.18431186676025</v>
       </c>
       <c r="J38" t="n">
-        <v>11.00043559074402</v>
+        <v>12.83962845802307</v>
       </c>
       <c r="K38" t="n">
-        <v>13.63054537773132</v>
+        <v>17.85946464538574</v>
       </c>
       <c r="L38" t="n">
-        <v>11.58956036567688</v>
+        <v>13.34077353477478</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>10.18750095367432</v>
+        <v>11.26812219619751</v>
       </c>
       <c r="C39" t="n">
-        <v>10.40841960906982</v>
+        <v>13.74190306663513</v>
       </c>
       <c r="D39" t="n">
-        <v>11.01735496520996</v>
+        <v>11.47412776947021</v>
       </c>
       <c r="E39" t="n">
-        <v>10.21744728088379</v>
+        <v>10.63471698760986</v>
       </c>
       <c r="F39" t="n">
-        <v>10.07530522346497</v>
+        <v>10.82327723503113</v>
       </c>
       <c r="G39" t="n">
-        <v>10.46625471115112</v>
+        <v>10.9854691028595</v>
       </c>
       <c r="H39" t="n">
-        <v>10.7855396270752</v>
+        <v>11.09429335594177</v>
       </c>
       <c r="I39" t="n">
-        <v>11.85580205917358</v>
+        <v>11.15183138847351</v>
       </c>
       <c r="J39" t="n">
-        <v>10.98402261734009</v>
+        <v>13.58222150802612</v>
       </c>
       <c r="K39" t="n">
-        <v>10.17260551452637</v>
+        <v>11.50009655952454</v>
       </c>
       <c r="L39" t="n">
-        <v>10.61702525615692</v>
+        <v>11.62560591697693</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>12.04683232307434</v>
+        <v>14.80949282646179</v>
       </c>
       <c r="C40" t="n">
-        <v>12.26077437400818</v>
+        <v>14.51862621307373</v>
       </c>
       <c r="D40" t="n">
-        <v>13.15001320838928</v>
+        <v>15.99558925628662</v>
       </c>
       <c r="E40" t="n">
-        <v>11.6837854385376</v>
+        <v>13.04580760002136</v>
       </c>
       <c r="F40" t="n">
-        <v>11.55206441879272</v>
+        <v>12.96222805976868</v>
       </c>
       <c r="G40" t="n">
-        <v>11.65929794311523</v>
+        <v>13.81907486915588</v>
       </c>
       <c r="H40" t="n">
-        <v>11.30243873596191</v>
+        <v>12.78105211257935</v>
       </c>
       <c r="I40" t="n">
-        <v>11.88659906387329</v>
+        <v>13.68393969535828</v>
       </c>
       <c r="J40" t="n">
-        <v>11.8362238407135</v>
+        <v>12.23462224006653</v>
       </c>
       <c r="K40" t="n">
-        <v>11.31422209739685</v>
+        <v>14.26611399650574</v>
       </c>
       <c r="L40" t="n">
-        <v>11.86922514438629</v>
+        <v>13.8116546869278</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>13.73596715927124</v>
+        <v>11.10486745834351</v>
       </c>
       <c r="C41" t="n">
-        <v>13.48564910888672</v>
+        <v>13.52734541893005</v>
       </c>
       <c r="D41" t="n">
-        <v>10.65637707710266</v>
+        <v>12.73308658599854</v>
       </c>
       <c r="E41" t="n">
-        <v>10.37716174125671</v>
+        <v>11.11682915687561</v>
       </c>
       <c r="F41" t="n">
-        <v>13.06673240661621</v>
+        <v>12.6559910774231</v>
       </c>
       <c r="G41" t="n">
-        <v>10.59306073188782</v>
+        <v>14.21343755722046</v>
       </c>
       <c r="H41" t="n">
-        <v>14.71815013885498</v>
+        <v>12.49006843566895</v>
       </c>
       <c r="I41" t="n">
-        <v>14.30209684371948</v>
+        <v>13.95242428779602</v>
       </c>
       <c r="J41" t="n">
-        <v>10.99189972877502</v>
+        <v>11.08569812774658</v>
       </c>
       <c r="K41" t="n">
-        <v>9.441483974456787</v>
+        <v>12.60070586204529</v>
       </c>
       <c r="L41" t="n">
-        <v>12.13685789108276</v>
+        <v>12.54804539680481</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>12.44961810112</v>
+        <v>13.77615976333618</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09597516059875</v>
+        <v>13.75170230865479</v>
       </c>
       <c r="D42" t="n">
-        <v>14.77460885047913</v>
+        <v>12.97442269325256</v>
       </c>
       <c r="E42" t="n">
-        <v>11.65267419815063</v>
+        <v>14.69182991981506</v>
       </c>
       <c r="F42" t="n">
-        <v>11.96936297416687</v>
+        <v>12.88261008262634</v>
       </c>
       <c r="G42" t="n">
-        <v>12.12797045707703</v>
+        <v>12.91524124145508</v>
       </c>
       <c r="H42" t="n">
-        <v>10.58010935783386</v>
+        <v>13.22948551177979</v>
       </c>
       <c r="I42" t="n">
-        <v>12.18401622772217</v>
+        <v>13.01913785934448</v>
       </c>
       <c r="J42" t="n">
-        <v>11.61894249916077</v>
+        <v>17.44454765319824</v>
       </c>
       <c r="K42" t="n">
-        <v>10.79751658439636</v>
+        <v>12.19688081741333</v>
       </c>
       <c r="L42" t="n">
-        <v>12.12507944107056</v>
+        <v>13.68820178508759</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>12.05084466934204</v>
+        <v>13.46623468399048</v>
       </c>
       <c r="C43" t="n">
-        <v>12.10316467285156</v>
+        <v>15.96385431289673</v>
       </c>
       <c r="D43" t="n">
-        <v>14.2487165927887</v>
+        <v>15.12233662605286</v>
       </c>
       <c r="E43" t="n">
-        <v>12.32824039459229</v>
+        <v>12.68613576889038</v>
       </c>
       <c r="F43" t="n">
-        <v>11.85944223403931</v>
+        <v>12.79599714279175</v>
       </c>
       <c r="G43" t="n">
-        <v>12.27577042579651</v>
+        <v>13.74159717559814</v>
       </c>
       <c r="H43" t="n">
-        <v>11.20847201347351</v>
+        <v>12.16189908981323</v>
       </c>
       <c r="I43" t="n">
-        <v>11.25929594039917</v>
+        <v>12.76706790924072</v>
       </c>
       <c r="J43" t="n">
-        <v>12.402428150177</v>
+        <v>13.68481421470642</v>
       </c>
       <c r="K43" t="n">
-        <v>11.78702569007874</v>
+        <v>13.96459889411926</v>
       </c>
       <c r="L43" t="n">
-        <v>12.15234007835388</v>
+        <v>13.63545358181</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>15.63729357719421</v>
+        <v>13.06348848342896</v>
       </c>
       <c r="C44" t="n">
-        <v>16.76678204536438</v>
+        <v>19.43053388595581</v>
       </c>
       <c r="D44" t="n">
-        <v>14.40034627914429</v>
+        <v>13.76846385002136</v>
       </c>
       <c r="E44" t="n">
-        <v>11.00899291038513</v>
+        <v>14.2129602432251</v>
       </c>
       <c r="F44" t="n">
-        <v>11.85781669616699</v>
+        <v>13.9681282043457</v>
       </c>
       <c r="G44" t="n">
-        <v>12.28921031951904</v>
+        <v>13.04936408996582</v>
       </c>
       <c r="H44" t="n">
-        <v>11.88077759742737</v>
+        <v>15.95591521263123</v>
       </c>
       <c r="I44" t="n">
-        <v>12.26877927780151</v>
+        <v>13.09542512893677</v>
       </c>
       <c r="J44" t="n">
-        <v>12.69815111160278</v>
+        <v>13.31565427780151</v>
       </c>
       <c r="K44" t="n">
-        <v>13.00391173362732</v>
+        <v>13.42193913459778</v>
       </c>
       <c r="L44" t="n">
-        <v>13.1812061548233</v>
+        <v>14.328187251091</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>14.09462833404541</v>
+        <v>11.63407063484192</v>
       </c>
       <c r="C45" t="n">
-        <v>13.40336084365845</v>
+        <v>11.15862846374512</v>
       </c>
       <c r="D45" t="n">
-        <v>11.17754697799683</v>
+        <v>11.85697484016418</v>
       </c>
       <c r="E45" t="n">
-        <v>10.34214496612549</v>
+        <v>14.16361451148987</v>
       </c>
       <c r="F45" t="n">
-        <v>10.63618850708008</v>
+        <v>11.13445496559143</v>
       </c>
       <c r="G45" t="n">
-        <v>11.29412889480591</v>
+        <v>11.30073261260986</v>
       </c>
       <c r="H45" t="n">
-        <v>10.46128439903259</v>
+        <v>11.90530681610107</v>
       </c>
       <c r="I45" t="n">
-        <v>12.92655658721924</v>
+        <v>11.83557271957397</v>
       </c>
       <c r="J45" t="n">
-        <v>10.91769242286682</v>
+        <v>10.52440881729126</v>
       </c>
       <c r="K45" t="n">
-        <v>10.586097240448</v>
+        <v>11.52045106887817</v>
       </c>
       <c r="L45" t="n">
-        <v>11.58396291732788</v>
+        <v>11.70342154502869</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>12.1685357093811</v>
+        <v>15.39737343788147</v>
       </c>
       <c r="C46" t="n">
-        <v>11.50321769714355</v>
+        <v>13.08967280387878</v>
       </c>
       <c r="D46" t="n">
-        <v>12.55288481712341</v>
+        <v>16.18441820144653</v>
       </c>
       <c r="E46" t="n">
-        <v>11.3400342464447</v>
+        <v>13.56847882270813</v>
       </c>
       <c r="F46" t="n">
-        <v>11.82029056549072</v>
+        <v>12.63481044769287</v>
       </c>
       <c r="G46" t="n">
-        <v>12.00677347183228</v>
+        <v>13.71341252326965</v>
       </c>
       <c r="H46" t="n">
-        <v>12.65905141830444</v>
+        <v>12.89007258415222</v>
       </c>
       <c r="I46" t="n">
-        <v>14.59806084632874</v>
+        <v>13.97215580940247</v>
       </c>
       <c r="J46" t="n">
-        <v>11.9694356918335</v>
+        <v>16.51432156562805</v>
       </c>
       <c r="K46" t="n">
-        <v>11.97647714614868</v>
+        <v>13.39353823661804</v>
       </c>
       <c r="L46" t="n">
-        <v>12.25947616100311</v>
+        <v>14.13582544326782</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>11.85680866241455</v>
+        <v>12.17171931266785</v>
       </c>
       <c r="C47" t="n">
-        <v>13.86919593811035</v>
+        <v>12.05228209495544</v>
       </c>
       <c r="D47" t="n">
-        <v>11.22842574119568</v>
+        <v>12.63132286071777</v>
       </c>
       <c r="E47" t="n">
-        <v>11.5630476474762</v>
+        <v>13.2677686214447</v>
       </c>
       <c r="F47" t="n">
-        <v>11.77054619789124</v>
+        <v>13.08137321472168</v>
       </c>
       <c r="G47" t="n">
-        <v>11.09925508499146</v>
+        <v>12.35309839248657</v>
       </c>
       <c r="H47" t="n">
-        <v>11.97850012779236</v>
+        <v>14.31369209289551</v>
       </c>
       <c r="I47" t="n">
-        <v>16.09198975563049</v>
+        <v>12.99981260299683</v>
       </c>
       <c r="J47" t="n">
-        <v>12.57302117347717</v>
+        <v>13.85421848297119</v>
       </c>
       <c r="K47" t="n">
-        <v>11.12620425224304</v>
+        <v>13.20353150367737</v>
       </c>
       <c r="L47" t="n">
-        <v>12.31569945812225</v>
+        <v>12.99288191795349</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>12.06727051734924</v>
+        <v>13.27332377433777</v>
       </c>
       <c r="C48" t="n">
-        <v>14.26235890388489</v>
+        <v>13.89256715774536</v>
       </c>
       <c r="D48" t="n">
-        <v>12.29724097251892</v>
+        <v>13.68466138839722</v>
       </c>
       <c r="E48" t="n">
-        <v>10.53564953804016</v>
+        <v>13.2402880191803</v>
       </c>
       <c r="F48" t="n">
-        <v>11.82390880584717</v>
+        <v>14.33715438842773</v>
       </c>
       <c r="G48" t="n">
-        <v>14.7237114906311</v>
+        <v>14.07050013542175</v>
       </c>
       <c r="H48" t="n">
-        <v>13.24854969978333</v>
+        <v>13.57963991165161</v>
       </c>
       <c r="I48" t="n">
-        <v>12.52893233299255</v>
+        <v>13.03357577323914</v>
       </c>
       <c r="J48" t="n">
-        <v>13.16828680038452</v>
+        <v>12.88228011131287</v>
       </c>
       <c r="K48" t="n">
-        <v>12.81368041038513</v>
+        <v>13.94937872886658</v>
       </c>
       <c r="L48" t="n">
-        <v>12.7469589471817</v>
+        <v>13.59433693885803</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>11.13752794265747</v>
+        <v>12.796541929245</v>
       </c>
       <c r="C49" t="n">
-        <v>11.63922810554504</v>
+        <v>13.01346874237061</v>
       </c>
       <c r="D49" t="n">
-        <v>11.09682512283325</v>
+        <v>13.31404829025269</v>
       </c>
       <c r="E49" t="n">
-        <v>11.73469424247742</v>
+        <v>12.98062705993652</v>
       </c>
       <c r="F49" t="n">
-        <v>11.19350719451904</v>
+        <v>12.30986738204956</v>
       </c>
       <c r="G49" t="n">
-        <v>11.98250269889832</v>
+        <v>12.65495562553406</v>
       </c>
       <c r="H49" t="n">
-        <v>11.62094259262085</v>
+        <v>12.21709895133972</v>
       </c>
       <c r="I49" t="n">
-        <v>11.34512400627136</v>
+        <v>14.49132537841797</v>
       </c>
       <c r="J49" t="n">
-        <v>11.72805237770081</v>
+        <v>16.60537528991699</v>
       </c>
       <c r="K49" t="n">
-        <v>11.06927466392517</v>
+        <v>13.5880286693573</v>
       </c>
       <c r="L49" t="n">
-        <v>11.45476789474487</v>
+        <v>13.39713373184204</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>12.02574896812439</v>
+        <v>13.22173929214478</v>
       </c>
       <c r="C50" t="n">
-        <v>11.72199988365173</v>
+        <v>13.3252956867218</v>
       </c>
       <c r="D50" t="n">
-        <v>12.09606552124023</v>
+        <v>13.06793642044067</v>
       </c>
       <c r="E50" t="n">
-        <v>13.80820727348328</v>
+        <v>12.46583867073059</v>
       </c>
       <c r="F50" t="n">
-        <v>14.67994260787964</v>
+        <v>15.03440976142883</v>
       </c>
       <c r="G50" t="n">
-        <v>11.33665871620178</v>
+        <v>15.06910300254822</v>
       </c>
       <c r="H50" t="n">
-        <v>12.43102407455444</v>
+        <v>14.92759037017822</v>
       </c>
       <c r="I50" t="n">
-        <v>11.30770230293274</v>
+        <v>13.96721744537354</v>
       </c>
       <c r="J50" t="n">
-        <v>11.42098760604858</v>
+        <v>13.58788514137268</v>
       </c>
       <c r="K50" t="n">
-        <v>15.09057259559631</v>
+        <v>13.84008479118347</v>
       </c>
       <c r="L50" t="n">
-        <v>12.59189095497131</v>
+        <v>13.85071005821228</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>11.8577938079834</v>
+        <v>12.34712076187134</v>
       </c>
       <c r="C51" t="n">
-        <v>13.17300772666931</v>
+        <v>12.13196396827698</v>
       </c>
       <c r="D51" t="n">
-        <v>10.26435828208923</v>
+        <v>12.39474511146545</v>
       </c>
       <c r="E51" t="n">
-        <v>10.73919773101807</v>
+        <v>14.6056489944458</v>
       </c>
       <c r="F51" t="n">
-        <v>11.24540090560913</v>
+        <v>12.5596079826355</v>
       </c>
       <c r="G51" t="n">
-        <v>10.38355565071106</v>
+        <v>12.95880770683289</v>
       </c>
       <c r="H51" t="n">
-        <v>10.76508378982544</v>
+        <v>12.14308500289917</v>
       </c>
       <c r="I51" t="n">
-        <v>10.68536448478699</v>
+        <v>13.81865191459656</v>
       </c>
       <c r="J51" t="n">
-        <v>10.79004573822021</v>
+        <v>12.06109714508057</v>
       </c>
       <c r="K51" t="n">
-        <v>12.14365816116333</v>
+        <v>11.83511185646057</v>
       </c>
       <c r="L51" t="n">
-        <v>11.20474662780762</v>
+        <v>12.68558404445648</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.25836883544922</v>
+        <v>12.90519966125488</v>
       </c>
       <c r="C52" t="n">
-        <v>12.1949692773819</v>
+        <v>13.47536214828491</v>
       </c>
       <c r="D52" t="n">
-        <v>12.28391544342041</v>
+        <v>13.52591978549957</v>
       </c>
       <c r="E52" t="n">
-        <v>11.68350160121918</v>
+        <v>13.26499128818512</v>
       </c>
       <c r="F52" t="n">
-        <v>11.840000872612</v>
+        <v>13.27547273159027</v>
       </c>
       <c r="G52" t="n">
-        <v>12.06132897853851</v>
+        <v>13.04436352729797</v>
       </c>
       <c r="H52" t="n">
-        <v>11.87858991622925</v>
+        <v>13.06406967639923</v>
       </c>
       <c r="I52" t="n">
-        <v>12.26007180690765</v>
+        <v>12.85484387397766</v>
       </c>
       <c r="J52" t="n">
-        <v>12.25750193595886</v>
+        <v>13.2328918170929</v>
       </c>
       <c r="K52" t="n">
-        <v>12.14552793502808</v>
+        <v>13.29326872348785</v>
       </c>
       <c r="L52" t="n">
-        <v>12.0863776602745</v>
+        <v>13.19363832330704</v>
       </c>
     </row>
   </sheetData>
